--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -233,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -277,6 +277,9 @@
     </xf>
     <xf numFmtId="166" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -1055,7 +1058,7 @@
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Horas de atendimento no mês</t>
+          <t>Horas de atendimento planejadas no mês</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -1105,626 +1108,632 @@
       </c>
       <c r="J5" s="14" t="n"/>
     </row>
-    <row r="6"/>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>A base do custo-hora são as horas de atendimento PLANEJADAS do mês (turnos × 4,33 semanas): é o preço que cobre o custo quando a agenda está cheia, e é ele que as planilhas 06, 07 e 08 usam. Como a agenda real nunca fica 100 % cheia, o bloco "Sensibilidade", no fim desta tela, mostra o custo-hora com as horas de fato atendidas (a última linha usa agosto, da planilha 01): é o número da conversa sobre faltas e horários vazios, não o da tabela de preços.</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Como chegamos ao número</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Passo</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>De onde vem</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Custos fixos do mês</t>
         </is>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="24">
         <f>'Custos fixos'!B36</f>
         <v>10000</v>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Aba Custos fixos</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n"/>
-      <c r="E9" s="25" t="n"/>
-      <c r="F9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="27" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Pró-labore e salários fora dos custos fixos (de quem entra no custo-hora)</t>
         </is>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="24">
         <f>SUMIFS(Equipe!$D$5:$D$14,Equipe!$E$5:$E$14,"Não",Equipe!$G$5:$G$14,"Sim")</f>
         <v>18000</v>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Aba Equipe: marcados "Entra no custo-hora? = Sim" e "Já está nos custos fixos? = Não"</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n"/>
-      <c r="E10" s="25" t="n"/>
-      <c r="F10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="27" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>Custo total do mês</t>
         </is>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="28">
         <f>B9+B10</f>
         <v>28000</v>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Soma dos dois acima</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="27" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>Horas de atendimento no mês (quem entra no custo-hora)</t>
-        </is>
-      </c>
-      <c r="B12" s="28">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Horas de atendimento planejadas no mês (quem entra no custo-hora)</t>
+        </is>
+      </c>
+      <c r="B12" s="29">
         <f>SUMIFS(Equipe!$F$5:$F$14,Equipe!$G$5:$G$14,"Sim")</f>
         <v>140</v>
       </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>Aba Equipe</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="26" t="n"/>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Aba Equipe: turnos da semana × 4,33 semanas</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Custo da hora de atendimento</t>
         </is>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="28">
         <f>IF(B12=0,"",B11/B12)</f>
         <v>200</v>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Custo total ÷ horas de atendimento</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="27" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Margem mínima sobre o preço</t>
         </is>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <f>Config!$B$7</f>
         <v>0.3</v>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="26" t="n"/>
+      <c r="F14" s="27" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>Impostos e taxas sobre o que entra</t>
-        </is>
-      </c>
-      <c r="B15" s="29">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Impostos sobre o que entra</t>
+        </is>
+      </c>
+      <c r="B15" s="30">
         <f>Config!$B$8</f>
         <v>0.11</v>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="27" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar (exata)</t>
         </is>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="24">
         <f>IF(B13="","",IFERROR(B13/(1-Config!$B$7-Config!$B$8),""))</f>
         <v>338.983050847458</v>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>Custo-hora ÷ (1 − margem − impostos)</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="27" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar (arredondada)</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="28">
         <f>IF(B16="","",CEILING(B16,Config!$B$9))</f>
         <v>340</v>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>Arredondada para cima, no múltiplo de Config</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="27" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Custo direto médio por hora (pró-labore ÷ horas)</t>
         </is>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="24">
         <f>IF(B12=0,0,B10/B12)</f>
         <v>128.571428571429</v>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>O que os sócios custam por hora de agenda</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="27" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>Custos indiretos (custos fixos, com a recepção)</t>
         </is>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="24">
         <f>B9</f>
         <v>10000</v>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>Para ratear por hora de atendimento</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="27" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Custo indireto por hora de atendimento</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="24">
         <f>IF(B12=0,0,B19/B12)</f>
         <v>71.4285714285714</v>
       </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>Custos fixos ÷ horas de atendimento (estrutura, recepção, aluguel)</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="26" t="n"/>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Custos fixos ÷ horas de atendimento (estrutura, recepção, aluguel). Já está dentro do custo-hora acima: na 11 serve só para mostrar quanto vale a hora de sala</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="27" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>Custo de um horário vazio (consulta de Config, em minutos)</t>
         </is>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="24">
         <f>IF(B13="","",B13*Config!$B$10/60)</f>
         <v>100</v>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>Custo-hora × duração da consulta: o que uma falta custa à clínica</t>
         </is>
       </c>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="27" t="n"/>
     </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Por pessoa</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Pessoa</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Papel</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>Remuneração</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>Horas de atendimento</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Horas planejadas</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>Custo direto por hora</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>Custo-hora completo</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="str">
+      <c r="A26" s="23" t="str">
         <f>IF(Equipe!$A$5="","",Equipe!$A$5)</f>
         <v>Dra. Carolina Mendes</v>
       </c>
-      <c r="B26" s="22" t="str">
+      <c r="B26" s="23" t="str">
         <f>IF(Equipe!$A$5="","",Equipe!$B$5)</f>
         <v>Sócia · clínica médica</v>
       </c>
-      <c r="C26" s="30" t="str">
+      <c r="C26" s="31" t="str">
         <f>IF(Equipe!$A$5="","",Equipe!$C$5)</f>
         <v>Pró-labore</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="29">
         <f>IF(Equipe!$A$5="","",IF(Equipe!$F$5="","",Equipe!$F$5))</f>
         <v>70</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="24">
         <f>IF(Equipe!$A$5="","",IF(Equipe!$H$5="","—",Equipe!$H$5))</f>
         <v>128.571428571429</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="24">
         <f>IF(Equipe!$A$5="","",IF(Equipe!$I$5="","—",Equipe!$I$5))</f>
         <v>200</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="24">
         <f>IF(Equipe!$A$5="","",IF(Equipe!$J$5="","—",Equipe!$J$5))</f>
         <v>338.983050847458</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="str">
+      <c r="A27" s="23" t="str">
         <f>IF(Equipe!$A$6="","",Equipe!$A$6)</f>
         <v>Dr. Paulo Andrade</v>
       </c>
-      <c r="B27" s="22" t="str">
+      <c r="B27" s="23" t="str">
         <f>IF(Equipe!$A$6="","",Equipe!$B$6)</f>
         <v>Sócio · cardiologia</v>
       </c>
-      <c r="C27" s="30" t="str">
+      <c r="C27" s="31" t="str">
         <f>IF(Equipe!$A$6="","",Equipe!$C$6)</f>
         <v>Pró-labore</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="29">
         <f>IF(Equipe!$A$6="","",IF(Equipe!$F$6="","",Equipe!$F$6))</f>
         <v>70</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="24">
         <f>IF(Equipe!$A$6="","",IF(Equipe!$H$6="","—",Equipe!$H$6))</f>
         <v>128.571428571429</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="24">
         <f>IF(Equipe!$A$6="","",IF(Equipe!$I$6="","—",Equipe!$I$6))</f>
         <v>200</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="24">
         <f>IF(Equipe!$A$6="","",IF(Equipe!$J$6="","—",Equipe!$J$6))</f>
         <v>338.983050847458</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="str">
+      <c r="A28" s="23" t="str">
         <f>IF(Equipe!$A$7="","",Equipe!$A$7)</f>
         <v>Dra. Renata Sousa</v>
       </c>
-      <c r="B28" s="22" t="str">
+      <c r="B28" s="23" t="str">
         <f>IF(Equipe!$A$7="","",Equipe!$B$7)</f>
         <v>Médica parceira · endocrinologia</v>
       </c>
-      <c r="C28" s="30" t="str">
+      <c r="C28" s="31" t="str">
         <f>IF(Equipe!$A$7="","",Equipe!$C$7)</f>
         <v>Repasse</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="29">
         <f>IF(Equipe!$A$7="","",IF(Equipe!$F$7="","",Equipe!$F$7))</f>
         <v>35</v>
       </c>
-      <c r="E28" s="23" t="str">
+      <c r="E28" s="24" t="str">
         <f>IF(Equipe!$A$7="","",IF(Equipe!$H$7="","—",Equipe!$H$7))</f>
         <v>—</v>
       </c>
-      <c r="F28" s="23" t="str">
+      <c r="F28" s="24" t="str">
         <f>IF(Equipe!$A$7="","",IF(Equipe!$I$7="","—",Equipe!$I$7))</f>
         <v>—</v>
       </c>
-      <c r="G28" s="23" t="str">
+      <c r="G28" s="24" t="str">
         <f>IF(Equipe!$A$7="","",IF(Equipe!$J$7="","—",Equipe!$J$7))</f>
         <v>—</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="str">
+      <c r="A29" s="23" t="str">
         <f>IF(Equipe!$A$8="","",Equipe!$A$8)</f>
         <v>Bruna Carvalho</v>
       </c>
-      <c r="B29" s="22" t="str">
+      <c r="B29" s="23" t="str">
         <f>IF(Equipe!$A$8="","",Equipe!$B$8)</f>
         <v>Recepcionista (CLT)</v>
       </c>
-      <c r="C29" s="30" t="str">
+      <c r="C29" s="31" t="str">
         <f>IF(Equipe!$A$8="","",Equipe!$C$8)</f>
         <v>Salário</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="29">
         <f>IF(Equipe!$A$8="","",IF(Equipe!$F$8="","",Equipe!$F$8))</f>
         <v/>
       </c>
-      <c r="E29" s="23" t="str">
+      <c r="E29" s="24" t="str">
         <f>IF(Equipe!$A$8="","",IF(Equipe!$H$8="","—",Equipe!$H$8))</f>
         <v>—</v>
       </c>
-      <c r="F29" s="23" t="str">
+      <c r="F29" s="24" t="str">
         <f>IF(Equipe!$A$8="","",IF(Equipe!$I$8="","—",Equipe!$I$8))</f>
         <v>—</v>
       </c>
-      <c r="G29" s="23" t="str">
+      <c r="G29" s="24" t="str">
         <f>IF(Equipe!$A$8="","",IF(Equipe!$J$8="","—",Equipe!$J$8))</f>
         <v>—</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22">
+      <c r="A30" s="23">
         <f>IF(Equipe!$A$9="","",Equipe!$A$9)</f>
         <v/>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="23">
         <f>IF(Equipe!$A$9="","",Equipe!$B$9)</f>
         <v/>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <f>IF(Equipe!$A$9="","",Equipe!$C$9)</f>
         <v/>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="29">
         <f>IF(Equipe!$A$9="","",IF(Equipe!$F$9="","",Equipe!$F$9))</f>
         <v/>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="24">
         <f>IF(Equipe!$A$9="","",IF(Equipe!$H$9="","—",Equipe!$H$9))</f>
         <v/>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="24">
         <f>IF(Equipe!$A$9="","",IF(Equipe!$I$9="","—",Equipe!$I$9))</f>
         <v/>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="24">
         <f>IF(Equipe!$A$9="","",IF(Equipe!$J$9="","—",Equipe!$J$9))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22">
+      <c r="A31" s="23">
         <f>IF(Equipe!$A$10="","",Equipe!$A$10)</f>
         <v/>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="23">
         <f>IF(Equipe!$A$10="","",Equipe!$B$10)</f>
         <v/>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <f>IF(Equipe!$A$10="","",Equipe!$C$10)</f>
         <v/>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="29">
         <f>IF(Equipe!$A$10="","",IF(Equipe!$F$10="","",Equipe!$F$10))</f>
         <v/>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="24">
         <f>IF(Equipe!$A$10="","",IF(Equipe!$H$10="","—",Equipe!$H$10))</f>
         <v/>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="24">
         <f>IF(Equipe!$A$10="","",IF(Equipe!$I$10="","—",Equipe!$I$10))</f>
         <v/>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="24">
         <f>IF(Equipe!$A$10="","",IF(Equipe!$J$10="","—",Equipe!$J$10))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22">
+      <c r="A32" s="23">
         <f>IF(Equipe!$A$11="","",Equipe!$A$11)</f>
         <v/>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="23">
         <f>IF(Equipe!$A$11="","",Equipe!$B$11)</f>
         <v/>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="31">
         <f>IF(Equipe!$A$11="","",Equipe!$C$11)</f>
         <v/>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="29">
         <f>IF(Equipe!$A$11="","",IF(Equipe!$F$11="","",Equipe!$F$11))</f>
         <v/>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="24">
         <f>IF(Equipe!$A$11="","",IF(Equipe!$H$11="","—",Equipe!$H$11))</f>
         <v/>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="24">
         <f>IF(Equipe!$A$11="","",IF(Equipe!$I$11="","—",Equipe!$I$11))</f>
         <v/>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="24">
         <f>IF(Equipe!$A$11="","",IF(Equipe!$J$11="","—",Equipe!$J$11))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22">
+      <c r="A33" s="23">
         <f>IF(Equipe!$A$12="","",Equipe!$A$12)</f>
         <v/>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="23">
         <f>IF(Equipe!$A$12="","",Equipe!$B$12)</f>
         <v/>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="31">
         <f>IF(Equipe!$A$12="","",Equipe!$C$12)</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="29">
         <f>IF(Equipe!$A$12="","",IF(Equipe!$F$12="","",Equipe!$F$12))</f>
         <v/>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="24">
         <f>IF(Equipe!$A$12="","",IF(Equipe!$H$12="","—",Equipe!$H$12))</f>
         <v/>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="24">
         <f>IF(Equipe!$A$12="","",IF(Equipe!$I$12="","—",Equipe!$I$12))</f>
         <v/>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="24">
         <f>IF(Equipe!$A$12="","",IF(Equipe!$J$12="","—",Equipe!$J$12))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22">
+      <c r="A34" s="23">
         <f>IF(Equipe!$A$13="","",Equipe!$A$13)</f>
         <v/>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="23">
         <f>IF(Equipe!$A$13="","",Equipe!$B$13)</f>
         <v/>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="31">
         <f>IF(Equipe!$A$13="","",Equipe!$C$13)</f>
         <v/>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="29">
         <f>IF(Equipe!$A$13="","",IF(Equipe!$F$13="","",Equipe!$F$13))</f>
         <v/>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="24">
         <f>IF(Equipe!$A$13="","",IF(Equipe!$H$13="","—",Equipe!$H$13))</f>
         <v/>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="24">
         <f>IF(Equipe!$A$13="","",IF(Equipe!$I$13="","—",Equipe!$I$13))</f>
         <v/>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="24">
         <f>IF(Equipe!$A$13="","",IF(Equipe!$J$13="","—",Equipe!$J$13))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22">
+      <c r="A35" s="23">
         <f>IF(Equipe!$A$14="","",Equipe!$A$14)</f>
         <v/>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="23">
         <f>IF(Equipe!$A$14="","",Equipe!$B$14)</f>
         <v/>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <f>IF(Equipe!$A$14="","",Equipe!$C$14)</f>
         <v/>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="29">
         <f>IF(Equipe!$A$14="","",IF(Equipe!$F$14="","",Equipe!$F$14))</f>
         <v/>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="24">
         <f>IF(Equipe!$A$14="","",IF(Equipe!$H$14="","—",Equipe!$H$14))</f>
         <v/>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="24">
         <f>IF(Equipe!$A$14="","",IF(Equipe!$I$14="","—",Equipe!$I$14))</f>
         <v/>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="24">
         <f>IF(Equipe!$A$14="","",IF(Equipe!$J$14="","—",Equipe!$J$14))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="31" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>Quem é pago por repasse ou já está nos custos fixos aparece com "—": não tem custo-hora próprio. O custo-hora completo de cada sócio = pró-labore ÷ horas + rateio da estrutura.</t>
         </is>
@@ -1732,180 +1741,180 @@
     </row>
     <row r="37"/>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>Sensibilidade: e se faltas e horários vazios tirarem horas do mês?</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>O custo fixo continua e cada hora atendida fica mais cara. Os percentuais em amarelo podem ser trocados; a última linha usa as horas atendidas de verdade (Painel da planilha 01, mês fechado).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>Cenário</t>
         </is>
       </c>
-      <c r="B40" s="21" t="inlineStr">
+      <c r="B40" s="22" t="inlineStr">
         <is>
           <t>Queda nas horas</t>
         </is>
       </c>
-      <c r="C40" s="21" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>Horas atendidas</t>
         </is>
       </c>
-      <c r="D40" s="21" t="inlineStr">
+      <c r="D40" s="22" t="inlineStr">
         <is>
           <t>Custo-hora</t>
         </is>
       </c>
-      <c r="E40" s="21" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
-      <c r="F40" s="21" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>Diferença por hora</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Agenda planejada</t>
         </is>
       </c>
-      <c r="B41" s="29" t="n">
+      <c r="B41" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <f>$B$12*(1-B41)</f>
         <v>140</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="24">
         <f>IF(C41=0,"",$B$11/C41)</f>
         <v>200</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="24">
         <f>IF(D41="","",IFERROR(D41/(1-Config!$B$7-Config!$B$8),""))</f>
         <v>338.983050847458</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="24">
         <f>IF(D41="","",D41-$D$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="str">
+      <c r="A42" s="23" t="str">
         <f>"Queda de "&amp;ROUND(B42*100,0)&amp;"%"</f>
         <v>Queda de 10%</v>
       </c>
-      <c r="B42" s="33" t="n">
+      <c r="B42" s="34" t="n">
         <v>0.1</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <f>$B$12*(1-B42)</f>
         <v>126</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="24">
         <f>IF(C42=0,"",$B$11/C42)</f>
         <v>222.222222222222</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="24">
         <f>IF(D42="","",IFERROR(D42/(1-Config!$B$7-Config!$B$8),""))</f>
         <v>376.647834274953</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="24">
         <f>IF(D42="","",D42-$D$41)</f>
         <v>22.2222222222222</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="str">
+      <c r="A43" s="23" t="str">
         <f>"Queda de "&amp;ROUND(B43*100,0)&amp;"%"</f>
         <v>Queda de 20%</v>
       </c>
-      <c r="B43" s="33" t="n">
+      <c r="B43" s="34" t="n">
         <v>0.2</v>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="33">
         <f>$B$12*(1-B43)</f>
         <v>112</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="24">
         <f>IF(C43=0,"",$B$11/C43)</f>
         <v>250</v>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="24">
         <f>IF(D43="","",IFERROR(D43/(1-Config!$B$7-Config!$B$8),""))</f>
         <v>423.728813559322</v>
       </c>
-      <c r="F43" s="23">
+      <c r="F43" s="24">
         <f>IF(D43="","",D43-$D$41)</f>
         <v>50</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="str">
+      <c r="A44" s="23" t="str">
         <f>"Queda de "&amp;ROUND(B44*100,0)&amp;"%"</f>
         <v>Queda de 30%</v>
       </c>
-      <c r="B44" s="33" t="n">
+      <c r="B44" s="34" t="n">
         <v>0.3</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <f>$B$12*(1-B44)</f>
         <v>98</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="24">
         <f>IF(C44=0,"",$B$11/C44)</f>
         <v>285.714285714286</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="24">
         <f>IF(D44="","",IFERROR(D44/(1-Config!$B$7-Config!$B$8),""))</f>
         <v>484.261501210654</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="24">
         <f>IF(D44="","",D44-$D$41)</f>
         <v>85.7142857142857</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>Agosto de 2026 realizado (horas atendidas dos sócios, planilha 01)</t>
-        </is>
-      </c>
-      <c r="B45" s="29">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>Agosto de 2026 realizado (horas atendidas dos sócios: Painel da 01 com Config = Agosto, coluna "Horas atendidas" da Dra. Carolina + do Dr. Paulo, sem a médica parceira)</t>
+        </is>
+      </c>
+      <c r="B45" s="30">
         <f>IF(C45="","",1-C45/$B$12)</f>
         <v>0.323571428571429</v>
       </c>
-      <c r="C45" s="34" t="n">
+      <c r="C45" s="35" t="n">
         <v>94.7</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="24">
         <f>IF(OR(C45="",C45=0),"",$B$11/C45)</f>
         <v>295.670538542767</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="24">
         <f>IF(D45="","",IFERROR(D45/(1-Config!$B$7-Config!$B$8),""))</f>
         <v>501.136506004689</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F45" s="24">
         <f>IF(D45="","",D45-$D$41)</f>
         <v>95.6705385427666</v>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="31" t="inlineStr">
+      <c r="A46" s="32" t="inlineStr">
         <is>
           <t>Planejado × realizado: a diferença entre o custo-hora de R$ 200 e o de agosto é o preço das faltas e dos horários vazios. Reduzir faltas (planilha 02) barateia a hora sem cortar nada.</t>
         </is>
@@ -1913,7 +1922,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
@@ -1929,6 +1938,7 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
@@ -1980,104 +1990,104 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>Nome da clínica</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Clínica Vida Plena (exemplo fictício)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Mês de referência</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Setembro de 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="38">
         <f>TODAY()</f>
         <v>46279.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Margem mínima sobre o preço (%)</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n">
+      <c r="B7" s="34" t="n">
         <v>0.3</v>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>Quanto do preço deve sobrar depois de pagar o custo da clínica. 30 % é um ponto de partida; ajuste ao seu mercado.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>Impostos e taxas sobre o que entra (%)</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="n">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>Impostos sobre o que entra (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="38" t="inlineStr">
-        <is>
-          <t>Percentual que sai de cada real recebido (impostos da PJ médica e taxas). No exemplo, 11 %: alíquota efetiva combinada com o contador (Simples, anexo III ou V, simplificado). Confira a sua com o contador.</t>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>Percentual de imposto que sai de cada real recebido pela PJ médica. No exemplo, 11 %: alíquota efetiva combinada com o contador (Simples, anexo III ou V, simplificado). Confira a sua com o contador. Só imposto: a taxa da maquininha NÃO entra aqui (ela é despesa variável, conciliada na 16 e lançada no caixa 09 e no resultado 18), e o convênio, que não passa na maquininha, pagaria a taxa sem dever.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Arredondar a hora mínima para múltiplos de (R$)</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>Só para o número ficar redondo na tabela de preços.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Duração de uma consulta (minutos), para o custo do horário vazio</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="41" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Custo da hora de atendimento = (custos fixos + pró-labore dos sócios) ÷ horas de atendimento planejadas no mês. Hora mínima = custo-hora ÷ (1 − margem − impostos): a margem é sobre o preço, não sobre o custo.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>No exemplo: R$ 28.000 ÷ 140 h = R$ 200,00; hora mínima R$ 338,98 → R$ 340. As planilhas 06, 07 e 08 usam este custo-hora. A médica parceira não entra: o repasse dela é custo variável (planilha 11).</t>
         </is>
@@ -2122,237 +2132,237 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Custo fixo</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Valor mensal (R$)</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Aluguel e condomínio</t>
         </is>
       </c>
-      <c r="B5" s="41" t="n">
+      <c r="B5" s="42" t="n">
         <v>3900</v>
       </c>
-      <c r="C5" s="36" t="n"/>
+      <c r="C5" s="37" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Recepção (salário e encargos)</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="42" t="n">
         <v>3100</v>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>Bruna Carvalho (CLT): a mesma pessoa da aba Equipe, marcada "Sim" lá</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Contador</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n">
+      <c r="B7" s="42" t="n">
         <v>600</v>
       </c>
-      <c r="C7" s="36" t="n"/>
+      <c r="C7" s="37" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Sistema de agenda e assinaturas</t>
         </is>
       </c>
-      <c r="B8" s="41" t="n">
+      <c r="B8" s="42" t="n">
         <v>300</v>
       </c>
-      <c r="C8" s="36" t="n"/>
+      <c r="C8" s="37" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Energia, água, internet e telefone</t>
         </is>
       </c>
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="42" t="n">
         <v>550</v>
       </c>
-      <c r="C9" s="36" t="n"/>
+      <c r="C9" s="37" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Limpeza e material de escritório</t>
         </is>
       </c>
-      <c r="B10" s="41" t="n">
+      <c r="B10" s="42" t="n">
         <v>450</v>
       </c>
-      <c r="C10" s="36" t="n"/>
+      <c r="C10" s="37" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Marketing e site</t>
         </is>
       </c>
-      <c r="B11" s="41" t="n">
+      <c r="B11" s="42" t="n">
         <v>650</v>
       </c>
-      <c r="C11" s="36" t="n"/>
+      <c r="C11" s="37" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Anuidade CRM, seguro e cursos</t>
         </is>
       </c>
-      <c r="B12" s="41" t="n">
+      <c r="B12" s="42" t="n">
         <v>450</v>
       </c>
-      <c r="C12" s="36" t="n"/>
+      <c r="C12" s="37" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="41" t="n"/>
-      <c r="C13" s="36" t="n"/>
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="37" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="41" t="n"/>
-      <c r="C14" s="36" t="n"/>
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="37" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="41" t="n"/>
-      <c r="C15" s="36" t="n"/>
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="37" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="41" t="n"/>
-      <c r="C16" s="36" t="n"/>
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="37" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="41" t="n"/>
-      <c r="C17" s="36" t="n"/>
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="37" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="41" t="n"/>
-      <c r="C18" s="36" t="n"/>
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="37" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="41" t="n"/>
-      <c r="C19" s="36" t="n"/>
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="37" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="41" t="n"/>
-      <c r="C20" s="36" t="n"/>
+      <c r="A20" s="37" t="n"/>
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="37" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="41" t="n"/>
-      <c r="C21" s="36" t="n"/>
+      <c r="A21" s="37" t="n"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="37" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="41" t="n"/>
-      <c r="C22" s="36" t="n"/>
+      <c r="A22" s="37" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="37" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="n"/>
-      <c r="B23" s="41" t="n"/>
-      <c r="C23" s="36" t="n"/>
+      <c r="A23" s="37" t="n"/>
+      <c r="B23" s="42" t="n"/>
+      <c r="C23" s="37" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="41" t="n"/>
-      <c r="C24" s="36" t="n"/>
+      <c r="A24" s="37" t="n"/>
+      <c r="B24" s="42" t="n"/>
+      <c r="C24" s="37" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="n"/>
-      <c r="B25" s="41" t="n"/>
-      <c r="C25" s="36" t="n"/>
+      <c r="A25" s="37" t="n"/>
+      <c r="B25" s="42" t="n"/>
+      <c r="C25" s="37" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="n"/>
-      <c r="B26" s="41" t="n"/>
-      <c r="C26" s="36" t="n"/>
+      <c r="A26" s="37" t="n"/>
+      <c r="B26" s="42" t="n"/>
+      <c r="C26" s="37" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="n"/>
-      <c r="B27" s="41" t="n"/>
-      <c r="C27" s="36" t="n"/>
+      <c r="A27" s="37" t="n"/>
+      <c r="B27" s="42" t="n"/>
+      <c r="C27" s="37" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="n"/>
-      <c r="B28" s="41" t="n"/>
-      <c r="C28" s="36" t="n"/>
+      <c r="A28" s="37" t="n"/>
+      <c r="B28" s="42" t="n"/>
+      <c r="C28" s="37" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="n"/>
-      <c r="B29" s="41" t="n"/>
-      <c r="C29" s="36" t="n"/>
+      <c r="A29" s="37" t="n"/>
+      <c r="B29" s="42" t="n"/>
+      <c r="C29" s="37" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="n"/>
-      <c r="B30" s="41" t="n"/>
-      <c r="C30" s="36" t="n"/>
+      <c r="A30" s="37" t="n"/>
+      <c r="B30" s="42" t="n"/>
+      <c r="C30" s="37" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="36" t="n"/>
-      <c r="B31" s="41" t="n"/>
-      <c r="C31" s="36" t="n"/>
+      <c r="A31" s="37" t="n"/>
+      <c r="B31" s="42" t="n"/>
+      <c r="C31" s="37" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="n"/>
-      <c r="B32" s="41" t="n"/>
-      <c r="C32" s="36" t="n"/>
+      <c r="A32" s="37" t="n"/>
+      <c r="B32" s="42" t="n"/>
+      <c r="C32" s="37" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="n"/>
-      <c r="B33" s="41" t="n"/>
-      <c r="C33" s="36" t="n"/>
+      <c r="A33" s="37" t="n"/>
+      <c r="B33" s="42" t="n"/>
+      <c r="C33" s="37" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="36" t="n"/>
-      <c r="B34" s="41" t="n"/>
-      <c r="C34" s="36" t="n"/>
+      <c r="A34" s="37" t="n"/>
+      <c r="B34" s="42" t="n"/>
+      <c r="C34" s="37" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="42" t="inlineStr">
+      <c r="A36" s="43" t="inlineStr">
         <is>
           <t>Total de custos fixos</t>
         </is>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="28">
         <f>SUM(B5:B34)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="38" t="inlineStr">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>Pró-labore dos sócios vai na aba Equipe. Salário da recepção com encargos fica aqui (e marcado "Sim" na Equipe, para não contar duas vezes). Materiais de atendimento, taxas de cartão e repasse não são fixos: ficam na precificação (06) e no caixa (09).</t>
         </is>
@@ -2404,370 +2414,370 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Pessoa</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Papel</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Remuneração</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>Valor mensal (R$)</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>Já está nos custos fixos?</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>Horas de atendimento no mês</t>
-        </is>
-      </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>Horas de atendimento planejadas no mês</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
         <is>
           <t>Entra no custo-hora?</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>Custo direto por hora</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>Custo-hora completo</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="J4" s="22" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Dra. Carolina Mendes</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Sócia · clínica médica</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Pró-labore</t>
         </is>
       </c>
-      <c r="D5" s="41" t="n">
+      <c r="D5" s="42" t="n">
         <v>9000</v>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="41" t="n">
         <v>70</v>
       </c>
-      <c r="G5" s="43" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="24">
         <f>IF(OR(A5="",G5&lt;&gt;"Sim",F5="",F5=0),"",IF(E5="Sim",0,D5)/F5)</f>
         <v>128.571428571429</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="24">
         <f>IF(H5="","",H5+Painel!$B$20)</f>
         <v>200</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="24">
         <f>IF(I5="","",IFERROR(I5/(1-Config!$B$7-Config!$B$8),""))</f>
         <v>338.983050847458</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Dr. Paulo Andrade</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Sócio · cardiologia</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>Pró-labore</t>
         </is>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="42" t="n">
         <v>9000</v>
       </c>
-      <c r="E6" s="43" t="inlineStr">
+      <c r="E6" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="41" t="n">
         <v>70</v>
       </c>
-      <c r="G6" s="43" t="inlineStr">
+      <c r="G6" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="24">
         <f>IF(OR(A6="",G6&lt;&gt;"Sim",F6="",F6=0),"",IF(E6="Sim",0,D6)/F6)</f>
         <v>128.571428571429</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="24">
         <f>IF(H6="","",H6+Painel!$B$20)</f>
         <v>200</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="24">
         <f>IF(I6="","",IFERROR(I6/(1-Config!$B$7-Config!$B$8),""))</f>
         <v>338.983050847458</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Médica parceira · endocrinologia</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>Repasse</t>
         </is>
       </c>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="43" t="inlineStr">
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="41" t="n">
         <v>35</v>
       </c>
-      <c r="G7" s="43" t="inlineStr">
+      <c r="G7" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="24">
         <f>IF(OR(A7="",G7&lt;&gt;"Sim",F7="",F7=0),"",IF(E7="Sim",0,D7)/F7)</f>
         <v/>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="24">
         <f>IF(H7="","",H7+Painel!$B$20)</f>
         <v/>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="24">
         <f>IF(I7="","",IFERROR(I7/(1-Config!$B$7-Config!$B$8),""))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Bruna Carvalho</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Recepcionista (CLT)</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>Salário</t>
         </is>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="42" t="n">
         <v>2200</v>
       </c>
-      <c r="E8" s="43" t="inlineStr">
+      <c r="E8" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F8" s="40" t="n"/>
-      <c r="G8" s="43" t="inlineStr">
+      <c r="F8" s="41" t="n"/>
+      <c r="G8" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="24">
         <f>IF(OR(A8="",G8&lt;&gt;"Sim",F8="",F8=0),"",IF(E8="Sim",0,D8)/F8)</f>
         <v/>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="24">
         <f>IF(H8="","",H8+Painel!$B$20)</f>
         <v/>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="24">
         <f>IF(I8="","",IFERROR(I8/(1-Config!$B$7-Config!$B$8),""))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="43" t="n"/>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="43" t="n"/>
-      <c r="F9" s="40" t="n"/>
-      <c r="G9" s="43" t="n"/>
-      <c r="H9" s="23">
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="42" t="n"/>
+      <c r="E9" s="44" t="n"/>
+      <c r="F9" s="41" t="n"/>
+      <c r="G9" s="44" t="n"/>
+      <c r="H9" s="24">
         <f>IF(OR(A9="",G9&lt;&gt;"Sim",F9="",F9=0),"",IF(E9="Sim",0,D9)/F9)</f>
         <v/>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="24">
         <f>IF(H9="","",H9+Painel!$B$20)</f>
         <v/>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="24">
         <f>IF(I9="","",IFERROR(I9/(1-Config!$B$7-Config!$B$8),""))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="43" t="n"/>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="43" t="n"/>
-      <c r="F10" s="40" t="n"/>
-      <c r="G10" s="43" t="n"/>
-      <c r="H10" s="23">
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="41" t="n"/>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="24">
         <f>IF(OR(A10="",G10&lt;&gt;"Sim",F10="",F10=0),"",IF(E10="Sim",0,D10)/F10)</f>
         <v/>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="24">
         <f>IF(H10="","",H10+Painel!$B$20)</f>
         <v/>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="24">
         <f>IF(I10="","",IFERROR(I10/(1-Config!$B$7-Config!$B$8),""))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="43" t="n"/>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="40" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="23">
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="42" t="n"/>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="41" t="n"/>
+      <c r="G11" s="44" t="n"/>
+      <c r="H11" s="24">
         <f>IF(OR(A11="",G11&lt;&gt;"Sim",F11="",F11=0),"",IF(E11="Sim",0,D11)/F11)</f>
         <v/>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="24">
         <f>IF(H11="","",H11+Painel!$B$20)</f>
         <v/>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="24">
         <f>IF(I11="","",IFERROR(I11/(1-Config!$B$7-Config!$B$8),""))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="43" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="40" t="n"/>
-      <c r="G12" s="43" t="n"/>
-      <c r="H12" s="23">
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="42" t="n"/>
+      <c r="E12" s="44" t="n"/>
+      <c r="F12" s="41" t="n"/>
+      <c r="G12" s="44" t="n"/>
+      <c r="H12" s="24">
         <f>IF(OR(A12="",G12&lt;&gt;"Sim",F12="",F12=0),"",IF(E12="Sim",0,D12)/F12)</f>
         <v/>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="24">
         <f>IF(H12="","",H12+Painel!$B$20)</f>
         <v/>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="24">
         <f>IF(I12="","",IFERROR(I12/(1-Config!$B$7-Config!$B$8),""))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="40" t="n"/>
-      <c r="G13" s="43" t="n"/>
-      <c r="H13" s="23">
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="41" t="n"/>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="24">
         <f>IF(OR(A13="",G13&lt;&gt;"Sim",F13="",F13=0),"",IF(E13="Sim",0,D13)/F13)</f>
         <v/>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="24">
         <f>IF(H13="","",H13+Painel!$B$20)</f>
         <v/>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="24">
         <f>IF(I13="","",IFERROR(I13/(1-Config!$B$7-Config!$B$8),""))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="43" t="n"/>
-      <c r="F14" s="40" t="n"/>
-      <c r="G14" s="43" t="n"/>
-      <c r="H14" s="23">
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="42" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="41" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="24">
         <f>IF(OR(A14="",G14&lt;&gt;"Sim",F14="",F14=0),"",IF(E14="Sim",0,D14)/F14)</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="24">
         <f>IF(H14="","",H14+Painel!$B$20)</f>
         <v/>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="24">
         <f>IF(I14="","",IFERROR(I14/(1-Config!$B$7-Config!$B$8),""))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Custo direto por hora = pró-labore ÷ horas de atendimento. Custo-hora completo = custo direto + rateio dos custos fixos por hora (calculado no Painel). Hora mínima = custo-hora completo ÷ (1 − margem − impostos).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
-        <is>
-          <t>Horas de atendimento planejadas: turnos da semana × 4,33 semanas (a planilha 01 mostra as disponíveis e as atendidas de verdade). Médico parceiro por repasse: "Entra no custo-hora? = Não"; a parte que fica com a clínica paga a estrutura que ele usa (planilha 11).</t>
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>Horas de atendimento planejadas: turnos da semana × 4,33 semanas (a planilha 01 mostra as disponíveis e as atendidas de verdade). Médico parceiro por repasse: "Entra no custo-hora? = Não". O custo da estrutura já está inteiro dentro do custo-hora dos sócios; por isso, na planilha 11, o custo indireto por hora entra só como informação e a margem da parceria desconta o material, não a estrutura de novo.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -20,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -263,19 +264,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -288,13 +289,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,14 +310,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -324,11 +325,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -336,7 +337,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -819,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -992,17 +993,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -2019,9 +2032,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="38">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B6" s="38" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="7">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -981,7 +981,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00B0A6C4"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="003B1F5E"/>
       <sz val="9"/>
@@ -98,6 +103,12 @@
       <b val="1"/>
       <color rgb="007A1F1F"/>
       <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007A1F1F"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -234,33 +245,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -273,16 +287,16 @@
     <xf numFmtId="167" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -346,6 +360,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1061,692 +1076,697 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="7">
+        <f>IF(SUM(Equipe!$K$5:$K$14)=0,"","Atenção: "&amp;SUM(Equipe!$K$5:$K$14)&amp;" pessoa(s) na aba Equipe (das que entram no custo-hora) sem valor mensal ou sem horas planejadas. Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: soma parcial daria custo-hora MENOR do que o real.")</f>
+        <v/>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Custo total do mês</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Horas de atendimento planejadas no mês</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Custo da hora de atendimento</t>
         </is>
       </c>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Custo de um horário vazio</t>
         </is>
       </c>
-      <c r="J4" s="14" t="n"/>
+      <c r="J4" s="15" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <f>B11</f>
         <v>28000</v>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="16">
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="17">
         <f>B12</f>
         <v>140</v>
       </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="17">
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="18">
         <f>B13</f>
         <v>200</v>
       </c>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="18">
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="19">
         <f>B17</f>
         <v>340</v>
       </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="19">
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="20">
         <f>B21</f>
         <v>100</v>
       </c>
-      <c r="J5" s="14" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>A base do custo-hora são as horas de atendimento PLANEJADAS do mês (turnos × 4,33 semanas): é o preço que cobre o custo quando a agenda está cheia, e é ele que as planilhas 06, 07 e 08 usam. Como a agenda real nunca fica 100 % cheia, o bloco "Sensibilidade", no fim desta tela, mostra o custo-hora com as horas de fato atendidas (a última linha usa agosto, da planilha 01): é o número da conversa sobre faltas e horários vazios, não o da tabela de preços.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Como chegamos ao número</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Passo</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>De onde vem</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Custos fixos do mês</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <f>'Custos fixos'!B36</f>
         <v>10000</v>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Aba Custos fixos</t>
         </is>
       </c>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="n"/>
-      <c r="F9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Pró-labore e salários fora dos custos fixos (de quem entra no custo-hora)</t>
         </is>
       </c>
-      <c r="B10" s="24">
-        <f>SUMIFS(Equipe!$D$5:$D$14,Equipe!$E$5:$E$14,"Não",Equipe!$G$5:$G$14,"Sim")</f>
+      <c r="B10" s="25">
+        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",SUMIFS(Equipe!$D$5:$D$14,Equipe!$E$5:$E$14,"Não",Equipe!$G$5:$G$14,"Sim"))</f>
         <v>18000</v>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Aba Equipe: marcados "Entra no custo-hora? = Sim" e "Já está nos custos fixos? = Não"</t>
         </is>
       </c>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Custo total do mês</t>
         </is>
       </c>
-      <c r="B11" s="28">
-        <f>B9+B10</f>
+      <c r="B11" s="29">
+        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",B9+B10)</f>
         <v>28000</v>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>Soma dos dois acima</t>
         </is>
       </c>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Horas de atendimento planejadas no mês (quem entra no custo-hora)</t>
         </is>
       </c>
-      <c r="B12" s="29">
-        <f>SUMIFS(Equipe!$F$5:$F$14,Equipe!$G$5:$G$14,"Sim")</f>
+      <c r="B12" s="30">
+        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",SUMIFS(Equipe!$F$5:$F$14,Equipe!$G$5:$G$14,"Sim"))</f>
         <v>140</v>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Aba Equipe: turnos da semana × 4,33 semanas</t>
         </is>
       </c>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Custo da hora de atendimento</t>
         </is>
       </c>
-      <c r="B13" s="28">
-        <f>IF(B12=0,"",B11/B12)</f>
+      <c r="B13" s="29">
+        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,"",B11/B12))</f>
         <v>200</v>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>Custo total ÷ horas de atendimento</t>
         </is>
       </c>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Margem mínima sobre o preço</t>
         </is>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <f>Config!$B$7</f>
         <v>0.3</v>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Impostos sobre o que entra</t>
         </is>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <f>Config!$B$8</f>
         <v>0.11</v>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar (exata)</t>
         </is>
       </c>
-      <c r="B16" s="24">
-        <f>IF(B13="","",IFERROR(B13/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="B16" s="25">
+        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",B13/(1-Config!$B$7-Config!$B$8))))</f>
         <v>338.983050847458</v>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Custo-hora ÷ (1 − margem − impostos)</t>
         </is>
       </c>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar (arredondada)</t>
         </is>
       </c>
-      <c r="B17" s="28">
-        <f>IF(B16="","",CEILING(B16,Config!$B$9))</f>
+      <c r="B17" s="29">
+        <f>IF(B16="","",IF(NOT(ISNUMBER(B16)),B16,CEILING(B16,Config!$B$9)))</f>
         <v>340</v>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Arredondada para cima, no múltiplo de Config</t>
         </is>
       </c>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Custo direto médio por hora (pró-labore ÷ horas)</t>
         </is>
       </c>
-      <c r="B18" s="24">
-        <f>IF(B12=0,0,B10/B12)</f>
+      <c r="B18" s="25">
+        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,0,B10/B12))</f>
         <v>128.571428571429</v>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>O que os sócios custam por hora de agenda</t>
         </is>
       </c>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Custos indiretos (custos fixos, com a recepção)</t>
         </is>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="25">
         <f>B9</f>
         <v>10000</v>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>Para ratear por hora de atendimento</t>
         </is>
       </c>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Custo indireto por hora de atendimento</t>
         </is>
       </c>
-      <c r="B20" s="24">
-        <f>IF(B12=0,0,B19/B12)</f>
+      <c r="B20" s="25">
+        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,0,B19/B12))</f>
         <v>71.4285714285714</v>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Custos fixos ÷ horas de atendimento (estrutura, recepção, aluguel). Já está dentro do custo-hora acima: na 11 serve só para mostrar quanto vale a hora de sala</t>
         </is>
       </c>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Custo de um horário vazio (consulta de Config, em minutos)</t>
         </is>
       </c>
-      <c r="B21" s="24">
-        <f>IF(B13="","",B13*Config!$B$10/60)</f>
+      <c r="B21" s="25">
+        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,B13*Config!$B$10/60))</f>
         <v>100</v>
       </c>
-      <c r="C21" s="25" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>Custo-hora × duração da consulta: o que uma falta custa à clínica</t>
         </is>
       </c>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
     </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Por pessoa</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>Pessoa</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>Papel</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>Remuneração</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>Horas planejadas</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>Custo direto por hora</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>Custo-hora completo</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="str">
+      <c r="A26" s="24" t="str">
         <f>IF(Equipe!$A$5="","",Equipe!$A$5)</f>
         <v>Dra. Carolina Mendes</v>
       </c>
-      <c r="B26" s="23" t="str">
+      <c r="B26" s="24" t="str">
         <f>IF(Equipe!$A$5="","",Equipe!$B$5)</f>
         <v>Sócia · clínica médica</v>
       </c>
-      <c r="C26" s="31" t="str">
+      <c r="C26" s="32" t="str">
         <f>IF(Equipe!$A$5="","",Equipe!$C$5)</f>
         <v>Pró-labore</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <f>IF(Equipe!$A$5="","",IF(Equipe!$F$5="","",Equipe!$F$5))</f>
         <v>70</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="25">
         <f>IF(Equipe!$A$5="","",IF(Equipe!$H$5="","—",Equipe!$H$5))</f>
         <v>128.571428571429</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="25">
         <f>IF(Equipe!$A$5="","",IF(Equipe!$I$5="","—",Equipe!$I$5))</f>
         <v>200</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="25">
         <f>IF(Equipe!$A$5="","",IF(Equipe!$J$5="","—",Equipe!$J$5))</f>
         <v>338.983050847458</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="str">
+      <c r="A27" s="24" t="str">
         <f>IF(Equipe!$A$6="","",Equipe!$A$6)</f>
         <v>Dr. Paulo Andrade</v>
       </c>
-      <c r="B27" s="23" t="str">
+      <c r="B27" s="24" t="str">
         <f>IF(Equipe!$A$6="","",Equipe!$B$6)</f>
         <v>Sócio · cardiologia</v>
       </c>
-      <c r="C27" s="31" t="str">
+      <c r="C27" s="32" t="str">
         <f>IF(Equipe!$A$6="","",Equipe!$C$6)</f>
         <v>Pró-labore</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <f>IF(Equipe!$A$6="","",IF(Equipe!$F$6="","",Equipe!$F$6))</f>
         <v>70</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="25">
         <f>IF(Equipe!$A$6="","",IF(Equipe!$H$6="","—",Equipe!$H$6))</f>
         <v>128.571428571429</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="25">
         <f>IF(Equipe!$A$6="","",IF(Equipe!$I$6="","—",Equipe!$I$6))</f>
         <v>200</v>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="25">
         <f>IF(Equipe!$A$6="","",IF(Equipe!$J$6="","—",Equipe!$J$6))</f>
         <v>338.983050847458</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="str">
+      <c r="A28" s="24" t="str">
         <f>IF(Equipe!$A$7="","",Equipe!$A$7)</f>
         <v>Dra. Renata Sousa</v>
       </c>
-      <c r="B28" s="23" t="str">
+      <c r="B28" s="24" t="str">
         <f>IF(Equipe!$A$7="","",Equipe!$B$7)</f>
         <v>Médica parceira · endocrinologia</v>
       </c>
-      <c r="C28" s="31" t="str">
+      <c r="C28" s="32" t="str">
         <f>IF(Equipe!$A$7="","",Equipe!$C$7)</f>
         <v>Repasse</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="30">
         <f>IF(Equipe!$A$7="","",IF(Equipe!$F$7="","",Equipe!$F$7))</f>
         <v>35</v>
       </c>
-      <c r="E28" s="24" t="str">
+      <c r="E28" s="25" t="str">
         <f>IF(Equipe!$A$7="","",IF(Equipe!$H$7="","—",Equipe!$H$7))</f>
         <v>—</v>
       </c>
-      <c r="F28" s="24" t="str">
+      <c r="F28" s="25" t="str">
         <f>IF(Equipe!$A$7="","",IF(Equipe!$I$7="","—",Equipe!$I$7))</f>
         <v>—</v>
       </c>
-      <c r="G28" s="24" t="str">
+      <c r="G28" s="25" t="str">
         <f>IF(Equipe!$A$7="","",IF(Equipe!$J$7="","—",Equipe!$J$7))</f>
         <v>—</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="str">
+      <c r="A29" s="24" t="str">
         <f>IF(Equipe!$A$8="","",Equipe!$A$8)</f>
         <v>Bruna Carvalho</v>
       </c>
-      <c r="B29" s="23" t="str">
+      <c r="B29" s="24" t="str">
         <f>IF(Equipe!$A$8="","",Equipe!$B$8)</f>
         <v>Recepcionista (CLT)</v>
       </c>
-      <c r="C29" s="31" t="str">
+      <c r="C29" s="32" t="str">
         <f>IF(Equipe!$A$8="","",Equipe!$C$8)</f>
         <v>Salário</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <f>IF(Equipe!$A$8="","",IF(Equipe!$F$8="","",Equipe!$F$8))</f>
         <v/>
       </c>
-      <c r="E29" s="24" t="str">
+      <c r="E29" s="25" t="str">
         <f>IF(Equipe!$A$8="","",IF(Equipe!$H$8="","—",Equipe!$H$8))</f>
         <v>—</v>
       </c>
-      <c r="F29" s="24" t="str">
+      <c r="F29" s="25" t="str">
         <f>IF(Equipe!$A$8="","",IF(Equipe!$I$8="","—",Equipe!$I$8))</f>
         <v>—</v>
       </c>
-      <c r="G29" s="24" t="str">
+      <c r="G29" s="25" t="str">
         <f>IF(Equipe!$A$8="","",IF(Equipe!$J$8="","—",Equipe!$J$8))</f>
         <v>—</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="23">
+      <c r="A30" s="24">
         <f>IF(Equipe!$A$9="","",Equipe!$A$9)</f>
         <v/>
       </c>
-      <c r="B30" s="23">
+      <c r="B30" s="24">
         <f>IF(Equipe!$A$9="","",Equipe!$B$9)</f>
         <v/>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="32">
         <f>IF(Equipe!$A$9="","",Equipe!$C$9)</f>
         <v/>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="30">
         <f>IF(Equipe!$A$9="","",IF(Equipe!$F$9="","",Equipe!$F$9))</f>
         <v/>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="25">
         <f>IF(Equipe!$A$9="","",IF(Equipe!$H$9="","—",Equipe!$H$9))</f>
         <v/>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="25">
         <f>IF(Equipe!$A$9="","",IF(Equipe!$I$9="","—",Equipe!$I$9))</f>
         <v/>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="25">
         <f>IF(Equipe!$A$9="","",IF(Equipe!$J$9="","—",Equipe!$J$9))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23">
+      <c r="A31" s="24">
         <f>IF(Equipe!$A$10="","",Equipe!$A$10)</f>
         <v/>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="24">
         <f>IF(Equipe!$A$10="","",Equipe!$B$10)</f>
         <v/>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="32">
         <f>IF(Equipe!$A$10="","",Equipe!$C$10)</f>
         <v/>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="30">
         <f>IF(Equipe!$A$10="","",IF(Equipe!$F$10="","",Equipe!$F$10))</f>
         <v/>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="25">
         <f>IF(Equipe!$A$10="","",IF(Equipe!$H$10="","—",Equipe!$H$10))</f>
         <v/>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="25">
         <f>IF(Equipe!$A$10="","",IF(Equipe!$I$10="","—",Equipe!$I$10))</f>
         <v/>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="25">
         <f>IF(Equipe!$A$10="","",IF(Equipe!$J$10="","—",Equipe!$J$10))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="23">
+      <c r="A32" s="24">
         <f>IF(Equipe!$A$11="","",Equipe!$A$11)</f>
         <v/>
       </c>
-      <c r="B32" s="23">
+      <c r="B32" s="24">
         <f>IF(Equipe!$A$11="","",Equipe!$B$11)</f>
         <v/>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="32">
         <f>IF(Equipe!$A$11="","",Equipe!$C$11)</f>
         <v/>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <f>IF(Equipe!$A$11="","",IF(Equipe!$F$11="","",Equipe!$F$11))</f>
         <v/>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="25">
         <f>IF(Equipe!$A$11="","",IF(Equipe!$H$11="","—",Equipe!$H$11))</f>
         <v/>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="25">
         <f>IF(Equipe!$A$11="","",IF(Equipe!$I$11="","—",Equipe!$I$11))</f>
         <v/>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="25">
         <f>IF(Equipe!$A$11="","",IF(Equipe!$J$11="","—",Equipe!$J$11))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="23">
+      <c r="A33" s="24">
         <f>IF(Equipe!$A$12="","",Equipe!$A$12)</f>
         <v/>
       </c>
-      <c r="B33" s="23">
+      <c r="B33" s="24">
         <f>IF(Equipe!$A$12="","",Equipe!$B$12)</f>
         <v/>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="32">
         <f>IF(Equipe!$A$12="","",Equipe!$C$12)</f>
         <v/>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="30">
         <f>IF(Equipe!$A$12="","",IF(Equipe!$F$12="","",Equipe!$F$12))</f>
         <v/>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="25">
         <f>IF(Equipe!$A$12="","",IF(Equipe!$H$12="","—",Equipe!$H$12))</f>
         <v/>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="25">
         <f>IF(Equipe!$A$12="","",IF(Equipe!$I$12="","—",Equipe!$I$12))</f>
         <v/>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="25">
         <f>IF(Equipe!$A$12="","",IF(Equipe!$J$12="","—",Equipe!$J$12))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23">
+      <c r="A34" s="24">
         <f>IF(Equipe!$A$13="","",Equipe!$A$13)</f>
         <v/>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="24">
         <f>IF(Equipe!$A$13="","",Equipe!$B$13)</f>
         <v/>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="32">
         <f>IF(Equipe!$A$13="","",Equipe!$C$13)</f>
         <v/>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="30">
         <f>IF(Equipe!$A$13="","",IF(Equipe!$F$13="","",Equipe!$F$13))</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="25">
         <f>IF(Equipe!$A$13="","",IF(Equipe!$H$13="","—",Equipe!$H$13))</f>
         <v/>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="25">
         <f>IF(Equipe!$A$13="","",IF(Equipe!$I$13="","—",Equipe!$I$13))</f>
         <v/>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="25">
         <f>IF(Equipe!$A$13="","",IF(Equipe!$J$13="","—",Equipe!$J$13))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23">
+      <c r="A35" s="24">
         <f>IF(Equipe!$A$14="","",Equipe!$A$14)</f>
         <v/>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="24">
         <f>IF(Equipe!$A$14="","",Equipe!$B$14)</f>
         <v/>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="32">
         <f>IF(Equipe!$A$14="","",Equipe!$C$14)</f>
         <v/>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="30">
         <f>IF(Equipe!$A$14="","",IF(Equipe!$F$14="","",Equipe!$F$14))</f>
         <v/>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="25">
         <f>IF(Equipe!$A$14="","",IF(Equipe!$H$14="","—",Equipe!$H$14))</f>
         <v/>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="25">
         <f>IF(Equipe!$A$14="","",IF(Equipe!$I$14="","—",Equipe!$I$14))</f>
         <v/>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="25">
         <f>IF(Equipe!$A$14="","",IF(Equipe!$J$14="","—",Equipe!$J$14))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="inlineStr">
+      <c r="A36" s="33" t="inlineStr">
         <is>
           <t>Quem é pago por repasse ou já está nos custos fixos aparece com "—": não tem custo-hora próprio. O custo-hora completo de cada sócio = pró-labore ÷ horas + rateio da estrutura.</t>
         </is>
@@ -1754,180 +1774,180 @@
     </row>
     <row r="37"/>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>Sensibilidade: e se faltas e horários vazios tirarem horas do mês?</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>O custo fixo continua e cada hora atendida fica mais cara. Os percentuais em amarelo podem ser trocados; a última linha usa as horas atendidas de verdade (Painel da planilha 01, mês fechado).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>Cenário</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>Queda nas horas</t>
         </is>
       </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>Horas atendidas</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>Custo-hora</t>
         </is>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>Diferença por hora</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>Agenda planejada</t>
         </is>
       </c>
-      <c r="B41" s="30" t="n">
+      <c r="B41" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="33">
-        <f>$B$12*(1-B41)</f>
+      <c r="C41" s="34">
+        <f>IF(ISNUMBER($B$12),$B$12*(1-B41),"")</f>
         <v>140</v>
       </c>
-      <c r="D41" s="24">
-        <f>IF(C41=0,"",$B$11/C41)</f>
+      <c r="D41" s="25">
+        <f>IF(OR(C41="",C41=0,NOT(ISNUMBER($B$11))),"",$B$11/C41)</f>
         <v>200</v>
       </c>
-      <c r="E41" s="24">
-        <f>IF(D41="","",IFERROR(D41/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="E41" s="25">
+        <f>IF(D41="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D41/(1-Config!$B$7-Config!$B$8)))</f>
         <v>338.983050847458</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="25">
         <f>IF(D41="","",D41-$D$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="str">
+      <c r="A42" s="24" t="str">
         <f>"Queda de "&amp;ROUND(B42*100,0)&amp;"%"</f>
         <v>Queda de 10%</v>
       </c>
-      <c r="B42" s="34" t="n">
+      <c r="B42" s="35" t="n">
         <v>0.1</v>
       </c>
-      <c r="C42" s="33">
-        <f>$B$12*(1-B42)</f>
+      <c r="C42" s="34">
+        <f>IF(ISNUMBER($B$12),$B$12*(1-B42),"")</f>
         <v>126</v>
       </c>
-      <c r="D42" s="24">
-        <f>IF(C42=0,"",$B$11/C42)</f>
+      <c r="D42" s="25">
+        <f>IF(OR(C42="",C42=0,NOT(ISNUMBER($B$11))),"",$B$11/C42)</f>
         <v>222.222222222222</v>
       </c>
-      <c r="E42" s="24">
-        <f>IF(D42="","",IFERROR(D42/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="E42" s="25">
+        <f>IF(D42="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D42/(1-Config!$B$7-Config!$B$8)))</f>
         <v>376.647834274953</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="25">
         <f>IF(D42="","",D42-$D$41)</f>
         <v>22.2222222222222</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="str">
+      <c r="A43" s="24" t="str">
         <f>"Queda de "&amp;ROUND(B43*100,0)&amp;"%"</f>
         <v>Queda de 20%</v>
       </c>
-      <c r="B43" s="34" t="n">
+      <c r="B43" s="35" t="n">
         <v>0.2</v>
       </c>
-      <c r="C43" s="33">
-        <f>$B$12*(1-B43)</f>
+      <c r="C43" s="34">
+        <f>IF(ISNUMBER($B$12),$B$12*(1-B43),"")</f>
         <v>112</v>
       </c>
-      <c r="D43" s="24">
-        <f>IF(C43=0,"",$B$11/C43)</f>
+      <c r="D43" s="25">
+        <f>IF(OR(C43="",C43=0,NOT(ISNUMBER($B$11))),"",$B$11/C43)</f>
         <v>250</v>
       </c>
-      <c r="E43" s="24">
-        <f>IF(D43="","",IFERROR(D43/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="E43" s="25">
+        <f>IF(D43="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D43/(1-Config!$B$7-Config!$B$8)))</f>
         <v>423.728813559322</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="25">
         <f>IF(D43="","",D43-$D$41)</f>
         <v>50</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="str">
+      <c r="A44" s="24" t="str">
         <f>"Queda de "&amp;ROUND(B44*100,0)&amp;"%"</f>
         <v>Queda de 30%</v>
       </c>
-      <c r="B44" s="34" t="n">
+      <c r="B44" s="35" t="n">
         <v>0.3</v>
       </c>
-      <c r="C44" s="33">
-        <f>$B$12*(1-B44)</f>
+      <c r="C44" s="34">
+        <f>IF(ISNUMBER($B$12),$B$12*(1-B44),"")</f>
         <v>98</v>
       </c>
-      <c r="D44" s="24">
-        <f>IF(C44=0,"",$B$11/C44)</f>
+      <c r="D44" s="25">
+        <f>IF(OR(C44="",C44=0,NOT(ISNUMBER($B$11))),"",$B$11/C44)</f>
         <v>285.714285714286</v>
       </c>
-      <c r="E44" s="24">
-        <f>IF(D44="","",IFERROR(D44/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="E44" s="25">
+        <f>IF(D44="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D44/(1-Config!$B$7-Config!$B$8)))</f>
         <v>484.261501210654</v>
       </c>
-      <c r="F44" s="24">
+      <c r="F44" s="25">
         <f>IF(D44="","",D44-$D$41)</f>
         <v>85.7142857142857</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="24" t="inlineStr">
         <is>
           <t>Agosto de 2026 realizado (horas atendidas dos sócios: Painel da 01 com Config = Agosto, coluna "Horas atendidas" da Dra. Carolina + do Dr. Paulo, sem a médica parceira)</t>
         </is>
       </c>
-      <c r="B45" s="30">
-        <f>IF(C45="","",1-C45/$B$12)</f>
+      <c r="B45" s="31">
+        <f>IF(OR(C45="",NOT(ISNUMBER($B$12))),"",1-C45/$B$12)</f>
         <v>0.323571428571429</v>
       </c>
-      <c r="C45" s="35" t="n">
+      <c r="C45" s="36" t="n">
         <v>94.7</v>
       </c>
-      <c r="D45" s="24">
-        <f>IF(OR(C45="",C45=0),"",$B$11/C45)</f>
+      <c r="D45" s="25">
+        <f>IF(OR(C45="",C45=0,NOT(ISNUMBER($B$11))),"",$B$11/C45)</f>
         <v>295.670538542767</v>
       </c>
-      <c r="E45" s="24">
-        <f>IF(D45="","",IFERROR(D45/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="E45" s="25">
+        <f>IF(D45="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D45/(1-Config!$B$7-Config!$B$8)))</f>
         <v>501.136506004689</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="25">
         <f>IF(D45="","",D45-$D$41)</f>
         <v>95.6705385427666</v>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="32" t="inlineStr">
+      <c r="A46" s="33" t="inlineStr">
         <is>
           <t>Planejado × realizado: a diferença entre o custo-hora de R$ 200 e o de agosto é o preço das faltas e dos horários vazios. Reduzir faltas (planilha 02) barateia a hora sem cortar nada.</t>
         </is>
@@ -1935,7 +1955,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="32">
+  <mergeCells count="33">
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
@@ -1965,6 +1985,7 @@
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A3:J3"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="A2:J2"/>
@@ -2003,103 +2024,103 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Nome da clínica</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Clínica Vida Plena (exemplo fictício)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Mês de referência</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Setembro de 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n">
+      <c r="B6" s="39" t="n">
         <v>46279</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Margem mínima sobre o preço (%)</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="35" t="n">
         <v>0.3</v>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>Quanto do preço deve sobrar depois de pagar o custo da clínica. 30 % é um ponto de partida; ajuste ao seu mercado.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Impostos sobre o que entra (%)</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="35" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>Percentual de imposto que sai de cada real recebido pela PJ médica. No exemplo, 11 %: alíquota efetiva combinada com o contador (Simples, anexo III ou V, simplificado). Confira a sua com o contador. Só imposto: a taxa da maquininha NÃO entra aqui (ela é despesa variável, conciliada na 16 e lançada no caixa 09 e no resultado 18), e o convênio, que não passa na maquininha, pagaria a taxa sem dever.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Arredondar a hora mínima para múltiplos de (R$)</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>Só para o número ficar redondo na tabela de preços.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Duração de uma consulta (minutos), para o custo do horário vazio</t>
         </is>
       </c>
-      <c r="B10" s="41" t="n">
+      <c r="B10" s="42" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Custo da hora de atendimento = (custos fixos + pró-labore dos sócios) ÷ horas de atendimento planejadas no mês. Hora mínima = custo-hora ÷ (1 − margem − impostos): a margem é sobre o preço, não sobre o custo.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>No exemplo: R$ 28.000 ÷ 140 h = R$ 200,00; hora mínima R$ 338,98 → R$ 340. As planilhas 06, 07 e 08 usam este custo-hora. A médica parceira não entra: o repasse dela é custo variável (planilha 11).</t>
         </is>
@@ -2111,6 +2132,14 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem entre 0 % e 99 %, e margem + impostos abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
+      <formula1>=AND(ISNUMBER(B7),B7&gt;=0,B7&lt;1,B7+N(B8)&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e margem + impostos abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
+      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B7)&lt;1)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2144,237 +2173,237 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Custo fixo</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Valor mensal (R$)</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Aluguel e condomínio</t>
         </is>
       </c>
-      <c r="B5" s="42" t="n">
+      <c r="B5" s="43" t="n">
         <v>3900</v>
       </c>
-      <c r="C5" s="37" t="n"/>
+      <c r="C5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Recepção (salário e encargos)</t>
         </is>
       </c>
-      <c r="B6" s="42" t="n">
+      <c r="B6" s="43" t="n">
         <v>3100</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>Bruna Carvalho (CLT): a mesma pessoa da aba Equipe, marcada "Sim" lá</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Contador</t>
         </is>
       </c>
-      <c r="B7" s="42" t="n">
+      <c r="B7" s="43" t="n">
         <v>600</v>
       </c>
-      <c r="C7" s="37" t="n"/>
+      <c r="C7" s="38" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Sistema de agenda e assinaturas</t>
         </is>
       </c>
-      <c r="B8" s="42" t="n">
+      <c r="B8" s="43" t="n">
         <v>300</v>
       </c>
-      <c r="C8" s="37" t="n"/>
+      <c r="C8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Energia, água, internet e telefone</t>
         </is>
       </c>
-      <c r="B9" s="42" t="n">
+      <c r="B9" s="43" t="n">
         <v>550</v>
       </c>
-      <c r="C9" s="37" t="n"/>
+      <c r="C9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>Limpeza e material de escritório</t>
         </is>
       </c>
-      <c r="B10" s="42" t="n">
+      <c r="B10" s="43" t="n">
         <v>450</v>
       </c>
-      <c r="C10" s="37" t="n"/>
+      <c r="C10" s="38" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Marketing e site</t>
         </is>
       </c>
-      <c r="B11" s="42" t="n">
+      <c r="B11" s="43" t="n">
         <v>650</v>
       </c>
-      <c r="C11" s="37" t="n"/>
+      <c r="C11" s="38" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Anuidade CRM, seguro e cursos</t>
         </is>
       </c>
-      <c r="B12" s="42" t="n">
+      <c r="B12" s="43" t="n">
         <v>450</v>
       </c>
-      <c r="C12" s="37" t="n"/>
+      <c r="C12" s="38" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="n"/>
-      <c r="B13" s="42" t="n"/>
-      <c r="C13" s="37" t="n"/>
+      <c r="A13" s="38" t="n"/>
+      <c r="B13" s="43" t="n"/>
+      <c r="C13" s="38" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="n"/>
-      <c r="B14" s="42" t="n"/>
-      <c r="C14" s="37" t="n"/>
+      <c r="A14" s="38" t="n"/>
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="38" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="n"/>
-      <c r="B15" s="42" t="n"/>
-      <c r="C15" s="37" t="n"/>
+      <c r="A15" s="38" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="38" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="n"/>
-      <c r="B16" s="42" t="n"/>
-      <c r="C16" s="37" t="n"/>
+      <c r="A16" s="38" t="n"/>
+      <c r="B16" s="43" t="n"/>
+      <c r="C16" s="38" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="n"/>
-      <c r="B17" s="42" t="n"/>
-      <c r="C17" s="37" t="n"/>
+      <c r="A17" s="38" t="n"/>
+      <c r="B17" s="43" t="n"/>
+      <c r="C17" s="38" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="n"/>
-      <c r="B18" s="42" t="n"/>
-      <c r="C18" s="37" t="n"/>
+      <c r="A18" s="38" t="n"/>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="38" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="n"/>
-      <c r="B19" s="42" t="n"/>
-      <c r="C19" s="37" t="n"/>
+      <c r="A19" s="38" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="38" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="n"/>
-      <c r="B20" s="42" t="n"/>
-      <c r="C20" s="37" t="n"/>
+      <c r="A20" s="38" t="n"/>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="n"/>
-      <c r="B21" s="42" t="n"/>
-      <c r="C21" s="37" t="n"/>
+      <c r="A21" s="38" t="n"/>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="38" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="n"/>
-      <c r="B22" s="42" t="n"/>
-      <c r="C22" s="37" t="n"/>
+      <c r="A22" s="38" t="n"/>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="38" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="n"/>
-      <c r="B23" s="42" t="n"/>
-      <c r="C23" s="37" t="n"/>
+      <c r="A23" s="38" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="38" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="n"/>
-      <c r="B24" s="42" t="n"/>
-      <c r="C24" s="37" t="n"/>
+      <c r="A24" s="38" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="38" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="n"/>
-      <c r="B25" s="42" t="n"/>
-      <c r="C25" s="37" t="n"/>
+      <c r="A25" s="38" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="38" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="n"/>
-      <c r="B26" s="42" t="n"/>
-      <c r="C26" s="37" t="n"/>
+      <c r="A26" s="38" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="38" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="n"/>
-      <c r="B27" s="42" t="n"/>
-      <c r="C27" s="37" t="n"/>
+      <c r="A27" s="38" t="n"/>
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="38" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="n"/>
-      <c r="B28" s="42" t="n"/>
-      <c r="C28" s="37" t="n"/>
+      <c r="A28" s="38" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="38" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="n"/>
-      <c r="B29" s="42" t="n"/>
-      <c r="C29" s="37" t="n"/>
+      <c r="A29" s="38" t="n"/>
+      <c r="B29" s="43" t="n"/>
+      <c r="C29" s="38" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="n"/>
-      <c r="B30" s="42" t="n"/>
-      <c r="C30" s="37" t="n"/>
+      <c r="A30" s="38" t="n"/>
+      <c r="B30" s="43" t="n"/>
+      <c r="C30" s="38" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="n"/>
-      <c r="B31" s="42" t="n"/>
-      <c r="C31" s="37" t="n"/>
+      <c r="A31" s="38" t="n"/>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="38" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="n"/>
-      <c r="B32" s="42" t="n"/>
-      <c r="C32" s="37" t="n"/>
+      <c r="A32" s="38" t="n"/>
+      <c r="B32" s="43" t="n"/>
+      <c r="C32" s="38" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="n"/>
-      <c r="B33" s="42" t="n"/>
-      <c r="C33" s="37" t="n"/>
+      <c r="A33" s="38" t="n"/>
+      <c r="B33" s="43" t="n"/>
+      <c r="C33" s="38" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="n"/>
-      <c r="B34" s="42" t="n"/>
-      <c r="C34" s="37" t="n"/>
+      <c r="A34" s="38" t="n"/>
+      <c r="B34" s="43" t="n"/>
+      <c r="C34" s="38" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="43" t="inlineStr">
+      <c r="A36" s="44" t="inlineStr">
         <is>
           <t>Total de custos fixos</t>
         </is>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="29">
         <f>SUM(B5:B34)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>Pró-labore dos sócios vai na aba Equipe. Salário da recepção com encargos fica aqui (e marcado "Sim" na Equipe, para não contar duas vezes). Materiais de atendimento, taxas de cartão e repasse não são fixos: ficam na precificação (06) e no caixa (09).</t>
         </is>
@@ -2409,6 +2438,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2426,368 +2456,408 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Pessoa</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Papel</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Remuneração</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Valor mensal (R$)</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Já está nos custos fixos?</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Horas de atendimento planejadas no mês</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>Entra no custo-hora?</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t>Custo direto por hora</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>Custo-hora completo</t>
         </is>
       </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Dra. Carolina Mendes</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Sócia · clínica médica</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="45" t="inlineStr">
         <is>
           <t>Pró-labore</t>
         </is>
       </c>
-      <c r="D5" s="42" t="n">
+      <c r="D5" s="43" t="n">
         <v>9000</v>
       </c>
-      <c r="E5" s="44" t="inlineStr">
+      <c r="E5" s="45" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="F5" s="41" t="n">
+      <c r="F5" s="42" t="n">
         <v>70</v>
       </c>
-      <c r="G5" s="44" t="inlineStr">
+      <c r="G5" s="45" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H5" s="24">
-        <f>IF(OR(A5="",G5&lt;&gt;"Sim",F5="",F5=0),"",IF(E5="Sim",0,D5)/F5)</f>
+      <c r="H5" s="25">
+        <f>IF(OR(A5="",G5&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F5)),F5=0),"faltam as horas planejadas",IF(AND(E5&lt;&gt;"Sim",NOT(ISNUMBER(D5))),"falta o valor mensal",IF(E5="Sim",0,D5)/F5)))</f>
         <v>128.571428571429</v>
       </c>
-      <c r="I5" s="24">
-        <f>IF(H5="","",H5+Painel!$B$20)</f>
+      <c r="I5" s="25">
+        <f>IF(H5="","",IF(NOT(ISNUMBER(H5)),H5,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H5+Painel!$B$20)))</f>
         <v>200</v>
       </c>
-      <c r="J5" s="24">
-        <f>IF(I5="","",IFERROR(I5/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="J5" s="25">
+        <f>IF(I5="","",IF(NOT(ISNUMBER(I5)),I5,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I5/(1-Config!$B$7-Config!$B$8))))</f>
         <v>338.983050847458</v>
       </c>
+      <c r="K5" s="46">
+        <f>IF(AND(A5&lt;&gt;"",G5="Sim",OR(NOT(ISNUMBER(F5)),AND(E5&lt;&gt;"Sim",NOT(ISNUMBER(D5))))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Dr. Paulo Andrade</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>Sócio · cardiologia</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>Pró-labore</t>
         </is>
       </c>
-      <c r="D6" s="42" t="n">
+      <c r="D6" s="43" t="n">
         <v>9000</v>
       </c>
-      <c r="E6" s="44" t="inlineStr">
+      <c r="E6" s="45" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="F6" s="41" t="n">
+      <c r="F6" s="42" t="n">
         <v>70</v>
       </c>
-      <c r="G6" s="44" t="inlineStr">
+      <c r="G6" s="45" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H6" s="24">
-        <f>IF(OR(A6="",G6&lt;&gt;"Sim",F6="",F6=0),"",IF(E6="Sim",0,D6)/F6)</f>
+      <c r="H6" s="25">
+        <f>IF(OR(A6="",G6&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F6)),F6=0),"faltam as horas planejadas",IF(AND(E6&lt;&gt;"Sim",NOT(ISNUMBER(D6))),"falta o valor mensal",IF(E6="Sim",0,D6)/F6)))</f>
         <v>128.571428571429</v>
       </c>
-      <c r="I6" s="24">
-        <f>IF(H6="","",H6+Painel!$B$20)</f>
+      <c r="I6" s="25">
+        <f>IF(H6="","",IF(NOT(ISNUMBER(H6)),H6,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H6+Painel!$B$20)))</f>
         <v>200</v>
       </c>
-      <c r="J6" s="24">
-        <f>IF(I6="","",IFERROR(I6/(1-Config!$B$7-Config!$B$8),""))</f>
+      <c r="J6" s="25">
+        <f>IF(I6="","",IF(NOT(ISNUMBER(I6)),I6,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I6/(1-Config!$B$7-Config!$B$8))))</f>
         <v>338.983050847458</v>
       </c>
+      <c r="K6" s="46">
+        <f>IF(AND(A6&lt;&gt;"",G6="Sim",OR(NOT(ISNUMBER(F6)),AND(E6&lt;&gt;"Sim",NOT(ISNUMBER(D6))))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Dra. Renata Sousa</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>Médica parceira · endocrinologia</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="45" t="inlineStr">
         <is>
           <t>Repasse</t>
         </is>
       </c>
-      <c r="D7" s="42" t="n"/>
-      <c r="E7" s="44" t="inlineStr">
+      <c r="D7" s="43" t="n"/>
+      <c r="E7" s="45" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="F7" s="41" t="n">
+      <c r="F7" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="G7" s="44" t="inlineStr">
+      <c r="G7" s="45" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="H7" s="24">
-        <f>IF(OR(A7="",G7&lt;&gt;"Sim",F7="",F7=0),"",IF(E7="Sim",0,D7)/F7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="24">
-        <f>IF(H7="","",H7+Painel!$B$20)</f>
-        <v/>
-      </c>
-      <c r="J7" s="24">
-        <f>IF(I7="","",IFERROR(I7/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="H7" s="25">
+        <f>IF(OR(A7="",G7&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F7)),F7=0),"faltam as horas planejadas",IF(AND(E7&lt;&gt;"Sim",NOT(ISNUMBER(D7))),"falta o valor mensal",IF(E7="Sim",0,D7)/F7)))</f>
+        <v/>
+      </c>
+      <c r="I7" s="25">
+        <f>IF(H7="","",IF(NOT(ISNUMBER(H7)),H7,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H7+Painel!$B$20)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="25">
+        <f>IF(I7="","",IF(NOT(ISNUMBER(I7)),I7,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I7/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K7" s="46">
+        <f>IF(AND(A7&lt;&gt;"",G7="Sim",OR(NOT(ISNUMBER(F7)),AND(E7&lt;&gt;"Sim",NOT(ISNUMBER(D7))))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Bruna Carvalho</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Recepcionista (CLT)</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>Salário</t>
         </is>
       </c>
-      <c r="D8" s="42" t="n">
+      <c r="D8" s="43" t="n">
         <v>2200</v>
       </c>
-      <c r="E8" s="44" t="inlineStr">
+      <c r="E8" s="45" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F8" s="41" t="n"/>
-      <c r="G8" s="44" t="inlineStr">
+      <c r="F8" s="42" t="n"/>
+      <c r="G8" s="45" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="H8" s="24">
-        <f>IF(OR(A8="",G8&lt;&gt;"Sim",F8="",F8=0),"",IF(E8="Sim",0,D8)/F8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="24">
-        <f>IF(H8="","",H8+Painel!$B$20)</f>
-        <v/>
-      </c>
-      <c r="J8" s="24">
-        <f>IF(I8="","",IFERROR(I8/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="H8" s="25">
+        <f>IF(OR(A8="",G8&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F8)),F8=0),"faltam as horas planejadas",IF(AND(E8&lt;&gt;"Sim",NOT(ISNUMBER(D8))),"falta o valor mensal",IF(E8="Sim",0,D8)/F8)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="25">
+        <f>IF(H8="","",IF(NOT(ISNUMBER(H8)),H8,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H8+Painel!$B$20)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="25">
+        <f>IF(I8="","",IF(NOT(ISNUMBER(I8)),I8,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I8/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K8" s="46">
+        <f>IF(AND(A8&lt;&gt;"",G8="Sim",OR(NOT(ISNUMBER(F8)),AND(E8&lt;&gt;"Sim",NOT(ISNUMBER(D8))))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="n"/>
-      <c r="B9" s="37" t="n"/>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="42" t="n"/>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="41" t="n"/>
-      <c r="G9" s="44" t="n"/>
-      <c r="H9" s="24">
-        <f>IF(OR(A9="",G9&lt;&gt;"Sim",F9="",F9=0),"",IF(E9="Sim",0,D9)/F9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="24">
-        <f>IF(H9="","",H9+Painel!$B$20)</f>
-        <v/>
-      </c>
-      <c r="J9" s="24">
-        <f>IF(I9="","",IFERROR(I9/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="A9" s="38" t="n"/>
+      <c r="B9" s="38" t="n"/>
+      <c r="C9" s="45" t="n"/>
+      <c r="D9" s="43" t="n"/>
+      <c r="E9" s="45" t="n"/>
+      <c r="F9" s="42" t="n"/>
+      <c r="G9" s="45" t="n"/>
+      <c r="H9" s="25">
+        <f>IF(OR(A9="",G9&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F9)),F9=0),"faltam as horas planejadas",IF(AND(E9&lt;&gt;"Sim",NOT(ISNUMBER(D9))),"falta o valor mensal",IF(E9="Sim",0,D9)/F9)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="25">
+        <f>IF(H9="","",IF(NOT(ISNUMBER(H9)),H9,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H9+Painel!$B$20)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="25">
+        <f>IF(I9="","",IF(NOT(ISNUMBER(I9)),I9,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I9/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K9" s="46">
+        <f>IF(AND(A9&lt;&gt;"",G9="Sim",OR(NOT(ISNUMBER(F9)),AND(E9&lt;&gt;"Sim",NOT(ISNUMBER(D9))))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="n"/>
-      <c r="B10" s="37" t="n"/>
-      <c r="C10" s="44" t="n"/>
-      <c r="D10" s="42" t="n"/>
-      <c r="E10" s="44" t="n"/>
-      <c r="F10" s="41" t="n"/>
-      <c r="G10" s="44" t="n"/>
-      <c r="H10" s="24">
-        <f>IF(OR(A10="",G10&lt;&gt;"Sim",F10="",F10=0),"",IF(E10="Sim",0,D10)/F10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="24">
-        <f>IF(H10="","",H10+Painel!$B$20)</f>
-        <v/>
-      </c>
-      <c r="J10" s="24">
-        <f>IF(I10="","",IFERROR(I10/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="A10" s="38" t="n"/>
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="43" t="n"/>
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="42" t="n"/>
+      <c r="G10" s="45" t="n"/>
+      <c r="H10" s="25">
+        <f>IF(OR(A10="",G10&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F10)),F10=0),"faltam as horas planejadas",IF(AND(E10&lt;&gt;"Sim",NOT(ISNUMBER(D10))),"falta o valor mensal",IF(E10="Sim",0,D10)/F10)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="25">
+        <f>IF(H10="","",IF(NOT(ISNUMBER(H10)),H10,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H10+Painel!$B$20)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(I10="","",IF(NOT(ISNUMBER(I10)),I10,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I10/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="46">
+        <f>IF(AND(A10&lt;&gt;"",G10="Sim",OR(NOT(ISNUMBER(F10)),AND(E10&lt;&gt;"Sim",NOT(ISNUMBER(D10))))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="n"/>
-      <c r="B11" s="37" t="n"/>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="42" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="41" t="n"/>
-      <c r="G11" s="44" t="n"/>
-      <c r="H11" s="24">
-        <f>IF(OR(A11="",G11&lt;&gt;"Sim",F11="",F11=0),"",IF(E11="Sim",0,D11)/F11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="24">
-        <f>IF(H11="","",H11+Painel!$B$20)</f>
-        <v/>
-      </c>
-      <c r="J11" s="24">
-        <f>IF(I11="","",IFERROR(I11/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="A11" s="38" t="n"/>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="43" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="42" t="n"/>
+      <c r="G11" s="45" t="n"/>
+      <c r="H11" s="25">
+        <f>IF(OR(A11="",G11&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F11)),F11=0),"faltam as horas planejadas",IF(AND(E11&lt;&gt;"Sim",NOT(ISNUMBER(D11))),"falta o valor mensal",IF(E11="Sim",0,D11)/F11)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="25">
+        <f>IF(H11="","",IF(NOT(ISNUMBER(H11)),H11,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H11+Painel!$B$20)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="25">
+        <f>IF(I11="","",IF(NOT(ISNUMBER(I11)),I11,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I11/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K11" s="46">
+        <f>IF(AND(A11&lt;&gt;"",G11="Sim",OR(NOT(ISNUMBER(F11)),AND(E11&lt;&gt;"Sim",NOT(ISNUMBER(D11))))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="n"/>
-      <c r="B12" s="37" t="n"/>
-      <c r="C12" s="44" t="n"/>
-      <c r="D12" s="42" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="41" t="n"/>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="24">
-        <f>IF(OR(A12="",G12&lt;&gt;"Sim",F12="",F12=0),"",IF(E12="Sim",0,D12)/F12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="24">
-        <f>IF(H12="","",H12+Painel!$B$20)</f>
-        <v/>
-      </c>
-      <c r="J12" s="24">
-        <f>IF(I12="","",IFERROR(I12/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="A12" s="38" t="n"/>
+      <c r="B12" s="38" t="n"/>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="43" t="n"/>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="42" t="n"/>
+      <c r="G12" s="45" t="n"/>
+      <c r="H12" s="25">
+        <f>IF(OR(A12="",G12&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F12)),F12=0),"faltam as horas planejadas",IF(AND(E12&lt;&gt;"Sim",NOT(ISNUMBER(D12))),"falta o valor mensal",IF(E12="Sim",0,D12)/F12)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="25">
+        <f>IF(H12="","",IF(NOT(ISNUMBER(H12)),H12,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H12+Painel!$B$20)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="25">
+        <f>IF(I12="","",IF(NOT(ISNUMBER(I12)),I12,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I12/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K12" s="46">
+        <f>IF(AND(A12&lt;&gt;"",G12="Sim",OR(NOT(ISNUMBER(F12)),AND(E12&lt;&gt;"Sim",NOT(ISNUMBER(D12))))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="n"/>
-      <c r="B13" s="37" t="n"/>
-      <c r="C13" s="44" t="n"/>
-      <c r="D13" s="42" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="41" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="24">
-        <f>IF(OR(A13="",G13&lt;&gt;"Sim",F13="",F13=0),"",IF(E13="Sim",0,D13)/F13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="24">
-        <f>IF(H13="","",H13+Painel!$B$20)</f>
-        <v/>
-      </c>
-      <c r="J13" s="24">
-        <f>IF(I13="","",IFERROR(I13/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="A13" s="38" t="n"/>
+      <c r="B13" s="38" t="n"/>
+      <c r="C13" s="45" t="n"/>
+      <c r="D13" s="43" t="n"/>
+      <c r="E13" s="45" t="n"/>
+      <c r="F13" s="42" t="n"/>
+      <c r="G13" s="45" t="n"/>
+      <c r="H13" s="25">
+        <f>IF(OR(A13="",G13&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F13)),F13=0),"faltam as horas planejadas",IF(AND(E13&lt;&gt;"Sim",NOT(ISNUMBER(D13))),"falta o valor mensal",IF(E13="Sim",0,D13)/F13)))</f>
+        <v/>
+      </c>
+      <c r="I13" s="25">
+        <f>IF(H13="","",IF(NOT(ISNUMBER(H13)),H13,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H13+Painel!$B$20)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="25">
+        <f>IF(I13="","",IF(NOT(ISNUMBER(I13)),I13,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I13/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K13" s="46">
+        <f>IF(AND(A13&lt;&gt;"",G13="Sim",OR(NOT(ISNUMBER(F13)),AND(E13&lt;&gt;"Sim",NOT(ISNUMBER(D13))))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="n"/>
-      <c r="B14" s="37" t="n"/>
-      <c r="C14" s="44" t="n"/>
-      <c r="D14" s="42" t="n"/>
-      <c r="E14" s="44" t="n"/>
-      <c r="F14" s="41" t="n"/>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="24">
-        <f>IF(OR(A14="",G14&lt;&gt;"Sim",F14="",F14=0),"",IF(E14="Sim",0,D14)/F14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="24">
-        <f>IF(H14="","",H14+Painel!$B$20)</f>
-        <v/>
-      </c>
-      <c r="J14" s="24">
-        <f>IF(I14="","",IFERROR(I14/(1-Config!$B$7-Config!$B$8),""))</f>
-        <v/>
+      <c r="A14" s="38" t="n"/>
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="45" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="42" t="n"/>
+      <c r="G14" s="45" t="n"/>
+      <c r="H14" s="25">
+        <f>IF(OR(A14="",G14&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F14)),F14=0),"faltam as horas planejadas",IF(AND(E14&lt;&gt;"Sim",NOT(ISNUMBER(D14))),"falta o valor mensal",IF(E14="Sim",0,D14)/F14)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="25">
+        <f>IF(H14="","",IF(NOT(ISNUMBER(H14)),H14,IF(NOT(ISNUMBER(Painel!$B$20)),"cadastro incompleto",H14+Painel!$B$20)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="25">
+        <f>IF(I14="","",IF(NOT(ISNUMBER(I14)),I14,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I14/(1-Config!$B$7-Config!$B$8))))</f>
+        <v/>
+      </c>
+      <c r="K14" s="46">
+        <f>IF(AND(A14&lt;&gt;"",G14="Sim",OR(NOT(ISNUMBER(F14)),AND(E14&lt;&gt;"Sim",NOT(ISNUMBER(D14))))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Custo direto por hora = pró-labore ÷ horas de atendimento. Custo-hora completo = custo direto + rateio dos custos fixos por hora (calculado no Painel). Hora mínima = custo-hora completo ÷ (1 − margem − impostos).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Horas de atendimento planejadas: turnos da semana × 4,33 semanas (a planilha 01 mostra as disponíveis e as atendidas de verdade). Médico parceiro por repasse: "Entra no custo-hora? = Não". O custo da estrutura já está inteiro dentro do custo-hora dos sócios; por isso, na planilha 11, o custo indireto por hora entra só como informação e a margem da parceria desconta o material, não a estrutura de novo.</t>
         </is>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B16" s="25">
-        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",B13/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",B13/(1-Config!$B$7-Config!$B$8))))</f>
         <v>338.983050847458</v>
       </c>
       <c r="C16" s="26" t="inlineStr">
@@ -1837,7 +1837,7 @@
         <v>200</v>
       </c>
       <c r="E41" s="25">
-        <f>IF(D41="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D41/(1-Config!$B$7-Config!$B$8)))</f>
+        <f>IF(D41="","",IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",D41/(1-Config!$B$7-Config!$B$8)))</f>
         <v>338.983050847458</v>
       </c>
       <c r="F41" s="25">
@@ -1862,7 +1862,7 @@
         <v>222.222222222222</v>
       </c>
       <c r="E42" s="25">
-        <f>IF(D42="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D42/(1-Config!$B$7-Config!$B$8)))</f>
+        <f>IF(D42="","",IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",D42/(1-Config!$B$7-Config!$B$8)))</f>
         <v>376.647834274953</v>
       </c>
       <c r="F42" s="25">
@@ -1887,7 +1887,7 @@
         <v>250</v>
       </c>
       <c r="E43" s="25">
-        <f>IF(D43="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D43/(1-Config!$B$7-Config!$B$8)))</f>
+        <f>IF(D43="","",IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",D43/(1-Config!$B$7-Config!$B$8)))</f>
         <v>423.728813559322</v>
       </c>
       <c r="F43" s="25">
@@ -1912,7 +1912,7 @@
         <v>285.714285714286</v>
       </c>
       <c r="E44" s="25">
-        <f>IF(D44="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D44/(1-Config!$B$7-Config!$B$8)))</f>
+        <f>IF(D44="","",IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",D44/(1-Config!$B$7-Config!$B$8)))</f>
         <v>484.261501210654</v>
       </c>
       <c r="F44" s="25">
@@ -1938,7 +1938,7 @@
         <v>295.670538542767</v>
       </c>
       <c r="E45" s="25">
-        <f>IF(D45="","",IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",D45/(1-Config!$B$7-Config!$B$8)))</f>
+        <f>IF(D45="","",IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",D45/(1-Config!$B$7-Config!$B$8)))</f>
         <v>501.136506004689</v>
       </c>
       <c r="F45" s="25">
@@ -2112,6 +2112,22 @@
         <v>30</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>Margem e impostos conferem? (calculado)</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="str">
+        <f>IF(AND(ISNUMBER(B7),ISNUMBER(B8)),IF(AND(B7&gt;=0,B7&lt;1,B8&gt;=0,B8&lt;1,B7+B8&lt;1),"Sim","Não"),"Não")</f>
+        <v>Sim</v>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>"Não" suspende a hora mínima em todas as abas: cada percentual precisa ficar entre 0 % e 99 %, e margem + impostos abaixo de 100 %.</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="40" t="inlineStr">
         <is>
@@ -2548,7 +2564,7 @@
         <v>200</v>
       </c>
       <c r="J5" s="25">
-        <f>IF(I5="","",IF(NOT(ISNUMBER(I5)),I5,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I5/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I5="","",IF(NOT(ISNUMBER(I5)),I5,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I5/(1-Config!$B$7-Config!$B$8))))</f>
         <v>338.983050847458</v>
       </c>
       <c r="K5" s="46">
@@ -2597,7 +2613,7 @@
         <v>200</v>
       </c>
       <c r="J6" s="25">
-        <f>IF(I6="","",IF(NOT(ISNUMBER(I6)),I6,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I6/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I6="","",IF(NOT(ISNUMBER(I6)),I6,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I6/(1-Config!$B$7-Config!$B$8))))</f>
         <v>338.983050847458</v>
       </c>
       <c r="K6" s="46">
@@ -2644,7 +2660,7 @@
         <v/>
       </c>
       <c r="J7" s="25">
-        <f>IF(I7="","",IF(NOT(ISNUMBER(I7)),I7,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I7/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I7="","",IF(NOT(ISNUMBER(I7)),I7,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I7/(1-Config!$B$7-Config!$B$8))))</f>
         <v/>
       </c>
       <c r="K7" s="46">
@@ -2691,7 +2707,7 @@
         <v/>
       </c>
       <c r="J8" s="25">
-        <f>IF(I8="","",IF(NOT(ISNUMBER(I8)),I8,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I8/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I8="","",IF(NOT(ISNUMBER(I8)),I8,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I8/(1-Config!$B$7-Config!$B$8))))</f>
         <v/>
       </c>
       <c r="K8" s="46">
@@ -2716,7 +2732,7 @@
         <v/>
       </c>
       <c r="J9" s="25">
-        <f>IF(I9="","",IF(NOT(ISNUMBER(I9)),I9,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I9/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I9="","",IF(NOT(ISNUMBER(I9)),I9,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I9/(1-Config!$B$7-Config!$B$8))))</f>
         <v/>
       </c>
       <c r="K9" s="46">
@@ -2741,7 +2757,7 @@
         <v/>
       </c>
       <c r="J10" s="25">
-        <f>IF(I10="","",IF(NOT(ISNUMBER(I10)),I10,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I10/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I10="","",IF(NOT(ISNUMBER(I10)),I10,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I10/(1-Config!$B$7-Config!$B$8))))</f>
         <v/>
       </c>
       <c r="K10" s="46">
@@ -2766,7 +2782,7 @@
         <v/>
       </c>
       <c r="J11" s="25">
-        <f>IF(I11="","",IF(NOT(ISNUMBER(I11)),I11,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I11/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I11="","",IF(NOT(ISNUMBER(I11)),I11,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I11/(1-Config!$B$7-Config!$B$8))))</f>
         <v/>
       </c>
       <c r="K11" s="46">
@@ -2791,7 +2807,7 @@
         <v/>
       </c>
       <c r="J12" s="25">
-        <f>IF(I12="","",IF(NOT(ISNUMBER(I12)),I12,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I12/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I12="","",IF(NOT(ISNUMBER(I12)),I12,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I12/(1-Config!$B$7-Config!$B$8))))</f>
         <v/>
       </c>
       <c r="K12" s="46">
@@ -2816,7 +2832,7 @@
         <v/>
       </c>
       <c r="J13" s="25">
-        <f>IF(I13="","",IF(NOT(ISNUMBER(I13)),I13,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I13/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I13="","",IF(NOT(ISNUMBER(I13)),I13,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I13/(1-Config!$B$7-Config!$B$8))))</f>
         <v/>
       </c>
       <c r="K13" s="46">
@@ -2841,7 +2857,7 @@
         <v/>
       </c>
       <c r="J14" s="25">
-        <f>IF(I14="","",IF(NOT(ISNUMBER(I14)),I14,IF((1-Config!$B$7-Config!$B$8)&lt;=0,"margens inválidas (Config)",I14/(1-Config!$B$7-Config!$B$8))))</f>
+        <f>IF(I14="","",IF(NOT(ISNUMBER(I14)),I14,IF(Config!$B$11&lt;&gt;"Sim","margens inválidas (Config)",I14/(1-Config!$B$7-Config!$B$8))))</f>
         <v/>
       </c>
       <c r="K14" s="46">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -2150,10 +2150,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem entre 0 % e 99 %, e margem + impostos abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
-      <formula1>=AND(ISNUMBER(B7),B7&gt;=0,B7&lt;1,B7+N(B8)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B7),AND(B7&gt;=0,B7&lt;1,B7+N(B8)&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e margem + impostos abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
-      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B7)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B8),AND(B8&gt;=0,B8&lt;1,B8+N(B7)&lt;1),FALSE)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -1078,7 +1078,7 @@
     </row>
     <row r="3">
       <c r="A3" s="7">
-        <f>IF(SUM(Equipe!$K$5:$K$14)=0,"","Atenção: "&amp;SUM(Equipe!$K$5:$K$14)&amp;" pessoa(s) na aba Equipe (das que entram no custo-hora) sem valor mensal ou sem horas planejadas. Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: soma parcial daria custo-hora MENOR do que o real.")</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem valor numérico na aba Custos fixos. ","")&amp;IF(SUM(Equipe!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Equipe!$K$5:$K$14)&amp;" pessoa(s) na aba Equipe com valor mensal, horas ou marcação (entra no custo-hora? / já nos fixos?) em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: soma parcial daria custo-hora MENOR do que o real.")</f>
         <v/>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="B10" s="25">
-        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",SUMIFS(Equipe!$D$5:$D$14,Equipe!$E$5:$E$14,"Não",Equipe!$G$5:$G$14,"Sim"))</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",SUMIFS(Equipe!$D$5:$D$14,Equipe!$E$5:$E$14,"Não",Equipe!$G$5:$G$14,"Sim"))</f>
         <v>18000</v>
       </c>
       <c r="C10" s="26" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",B9+B10)</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",B9+B10)</f>
         <v>28000</v>
       </c>
       <c r="C11" s="26" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="B12" s="30">
-        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",SUMIFS(Equipe!$F$5:$F$14,Equipe!$G$5:$G$14,"Sim"))</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",SUMIFS(Equipe!$F$5:$F$14,Equipe!$G$5:$G$14,"Sim"))</f>
         <v>140</v>
       </c>
       <c r="C12" s="26" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="B13" s="29">
-        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,"",B11/B12))</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",IF(B12=0,"",B11/B12))</f>
         <v>200</v>
       </c>
       <c r="C13" s="26" t="inlineStr">
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B18" s="25">
-        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,0,B10/B12))</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",IF(B12=0,0,B10/B12))</f>
         <v>128.571428571429</v>
       </c>
       <c r="C18" s="26" t="inlineStr">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="B19" s="25">
-        <f>B9</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",B9)</f>
         <v>10000</v>
       </c>
       <c r="C19" s="26" t="inlineStr">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B20" s="25">
-        <f>IF(SUM(Equipe!$K$5:$K$14)&gt;0,"cadastro incompleto",IF(B12=0,0,B19/B12))</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))&gt;0,"cadastro incompleto",IF(B12=0,0,B19/B12))</f>
         <v>71.4285714285714</v>
       </c>
       <c r="C20" s="26" t="inlineStr">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="B36" s="29">
-        <f>SUM(B5:B34)</f>
+        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*(ISNUMBER(B5:B34)=FALSE))&gt;0,"custo fixo sem valor numérico",SUM(B5:B34))</f>
         <v>10000</v>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="H5" s="25">
-        <f>IF(OR(A5="",G5&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F5)),F5=0),"faltam as horas planejadas",IF(AND(E5&lt;&gt;"Sim",NOT(ISNUMBER(D5))),"falta o valor mensal",IF(E5="Sim",0,D5)/F5)))</f>
+        <f>IF(A5="","",IF(AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G5&lt;&gt;"Sim","",IF(AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F5)),F5=0),"faltam as horas planejadas",IF(AND(E5&lt;&gt;"Sim",NOT(ISNUMBER(D5))),"falta o valor mensal",IF(E5="Sim",0,D5)/F5))))))</f>
         <v>128.571428571429</v>
       </c>
       <c r="I5" s="25">
@@ -2568,7 +2568,7 @@
         <v>338.983050847458</v>
       </c>
       <c r="K5" s="46">
-        <f>IF(AND(A5&lt;&gt;"",G5="Sim",OR(NOT(ISNUMBER(F5)),AND(E5&lt;&gt;"Sim",NOT(ISNUMBER(D5))))),1,0)</f>
+        <f>IF(AND(A5&lt;&gt;"",OR(AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),AND(G5="Sim",OR(NOT(ISNUMBER(F5)),AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),AND(E5&lt;&gt;"Sim",NOT(ISNUMBER(D5))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="H6" s="25">
-        <f>IF(OR(A6="",G6&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F6)),F6=0),"faltam as horas planejadas",IF(AND(E6&lt;&gt;"Sim",NOT(ISNUMBER(D6))),"falta o valor mensal",IF(E6="Sim",0,D6)/F6)))</f>
+        <f>IF(A6="","",IF(AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G6&lt;&gt;"Sim","",IF(AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F6)),F6=0),"faltam as horas planejadas",IF(AND(E6&lt;&gt;"Sim",NOT(ISNUMBER(D6))),"falta o valor mensal",IF(E6="Sim",0,D6)/F6))))))</f>
         <v>128.571428571429</v>
       </c>
       <c r="I6" s="25">
@@ -2617,7 +2617,7 @@
         <v>338.983050847458</v>
       </c>
       <c r="K6" s="46">
-        <f>IF(AND(A6&lt;&gt;"",G6="Sim",OR(NOT(ISNUMBER(F6)),AND(E6&lt;&gt;"Sim",NOT(ISNUMBER(D6))))),1,0)</f>
+        <f>IF(AND(A6&lt;&gt;"",OR(AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),AND(G6="Sim",OR(NOT(ISNUMBER(F6)),AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),AND(E6&lt;&gt;"Sim",NOT(ISNUMBER(D6))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="H7" s="25">
-        <f>IF(OR(A7="",G7&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F7)),F7=0),"faltam as horas planejadas",IF(AND(E7&lt;&gt;"Sim",NOT(ISNUMBER(D7))),"falta o valor mensal",IF(E7="Sim",0,D7)/F7)))</f>
+        <f>IF(A7="","",IF(AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G7&lt;&gt;"Sim","",IF(AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F7)),F7=0),"faltam as horas planejadas",IF(AND(E7&lt;&gt;"Sim",NOT(ISNUMBER(D7))),"falta o valor mensal",IF(E7="Sim",0,D7)/F7))))))</f>
         <v/>
       </c>
       <c r="I7" s="25">
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="K7" s="46">
-        <f>IF(AND(A7&lt;&gt;"",G7="Sim",OR(NOT(ISNUMBER(F7)),AND(E7&lt;&gt;"Sim",NOT(ISNUMBER(D7))))),1,0)</f>
+        <f>IF(AND(A7&lt;&gt;"",OR(AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),AND(G7="Sim",OR(NOT(ISNUMBER(F7)),AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),AND(E7&lt;&gt;"Sim",NOT(ISNUMBER(D7))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="H8" s="25">
-        <f>IF(OR(A8="",G8&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F8)),F8=0),"faltam as horas planejadas",IF(AND(E8&lt;&gt;"Sim",NOT(ISNUMBER(D8))),"falta o valor mensal",IF(E8="Sim",0,D8)/F8)))</f>
+        <f>IF(A8="","",IF(AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G8&lt;&gt;"Sim","",IF(AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F8)),F8=0),"faltam as horas planejadas",IF(AND(E8&lt;&gt;"Sim",NOT(ISNUMBER(D8))),"falta o valor mensal",IF(E8="Sim",0,D8)/F8))))))</f>
         <v/>
       </c>
       <c r="I8" s="25">
@@ -2711,7 +2711,7 @@
         <v/>
       </c>
       <c r="K8" s="46">
-        <f>IF(AND(A8&lt;&gt;"",G8="Sim",OR(NOT(ISNUMBER(F8)),AND(E8&lt;&gt;"Sim",NOT(ISNUMBER(D8))))),1,0)</f>
+        <f>IF(AND(A8&lt;&gt;"",OR(AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),AND(G8="Sim",OR(NOT(ISNUMBER(F8)),AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),AND(E8&lt;&gt;"Sim",NOT(ISNUMBER(D8))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       <c r="F9" s="42" t="n"/>
       <c r="G9" s="45" t="n"/>
       <c r="H9" s="25">
-        <f>IF(OR(A9="",G9&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F9)),F9=0),"faltam as horas planejadas",IF(AND(E9&lt;&gt;"Sim",NOT(ISNUMBER(D9))),"falta o valor mensal",IF(E9="Sim",0,D9)/F9)))</f>
+        <f>IF(A9="","",IF(AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G9&lt;&gt;"Sim","",IF(AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F9)),F9=0),"faltam as horas planejadas",IF(AND(E9&lt;&gt;"Sim",NOT(ISNUMBER(D9))),"falta o valor mensal",IF(E9="Sim",0,D9)/F9))))))</f>
         <v/>
       </c>
       <c r="I9" s="25">
@@ -2736,7 +2736,7 @@
         <v/>
       </c>
       <c r="K9" s="46">
-        <f>IF(AND(A9&lt;&gt;"",G9="Sim",OR(NOT(ISNUMBER(F9)),AND(E9&lt;&gt;"Sim",NOT(ISNUMBER(D9))))),1,0)</f>
+        <f>IF(AND(A9&lt;&gt;"",OR(AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),AND(G9="Sim",OR(NOT(ISNUMBER(F9)),AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),AND(E9&lt;&gt;"Sim",NOT(ISNUMBER(D9))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       <c r="F10" s="42" t="n"/>
       <c r="G10" s="45" t="n"/>
       <c r="H10" s="25">
-        <f>IF(OR(A10="",G10&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F10)),F10=0),"faltam as horas planejadas",IF(AND(E10&lt;&gt;"Sim",NOT(ISNUMBER(D10))),"falta o valor mensal",IF(E10="Sim",0,D10)/F10)))</f>
+        <f>IF(A10="","",IF(AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G10&lt;&gt;"Sim","",IF(AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F10)),F10=0),"faltam as horas planejadas",IF(AND(E10&lt;&gt;"Sim",NOT(ISNUMBER(D10))),"falta o valor mensal",IF(E10="Sim",0,D10)/F10))))))</f>
         <v/>
       </c>
       <c r="I10" s="25">
@@ -2761,7 +2761,7 @@
         <v/>
       </c>
       <c r="K10" s="46">
-        <f>IF(AND(A10&lt;&gt;"",G10="Sim",OR(NOT(ISNUMBER(F10)),AND(E10&lt;&gt;"Sim",NOT(ISNUMBER(D10))))),1,0)</f>
+        <f>IF(AND(A10&lt;&gt;"",OR(AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),AND(G10="Sim",OR(NOT(ISNUMBER(F10)),AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),AND(E10&lt;&gt;"Sim",NOT(ISNUMBER(D10))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       <c r="F11" s="42" t="n"/>
       <c r="G11" s="45" t="n"/>
       <c r="H11" s="25">
-        <f>IF(OR(A11="",G11&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F11)),F11=0),"faltam as horas planejadas",IF(AND(E11&lt;&gt;"Sim",NOT(ISNUMBER(D11))),"falta o valor mensal",IF(E11="Sim",0,D11)/F11)))</f>
+        <f>IF(A11="","",IF(AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G11&lt;&gt;"Sim","",IF(AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F11)),F11=0),"faltam as horas planejadas",IF(AND(E11&lt;&gt;"Sim",NOT(ISNUMBER(D11))),"falta o valor mensal",IF(E11="Sim",0,D11)/F11))))))</f>
         <v/>
       </c>
       <c r="I11" s="25">
@@ -2786,7 +2786,7 @@
         <v/>
       </c>
       <c r="K11" s="46">
-        <f>IF(AND(A11&lt;&gt;"",G11="Sim",OR(NOT(ISNUMBER(F11)),AND(E11&lt;&gt;"Sim",NOT(ISNUMBER(D11))))),1,0)</f>
+        <f>IF(AND(A11&lt;&gt;"",OR(AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),AND(G11="Sim",OR(NOT(ISNUMBER(F11)),AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),AND(E11&lt;&gt;"Sim",NOT(ISNUMBER(D11))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       <c r="F12" s="42" t="n"/>
       <c r="G12" s="45" t="n"/>
       <c r="H12" s="25">
-        <f>IF(OR(A12="",G12&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F12)),F12=0),"faltam as horas planejadas",IF(AND(E12&lt;&gt;"Sim",NOT(ISNUMBER(D12))),"falta o valor mensal",IF(E12="Sim",0,D12)/F12)))</f>
+        <f>IF(A12="","",IF(AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G12&lt;&gt;"Sim","",IF(AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F12)),F12=0),"faltam as horas planejadas",IF(AND(E12&lt;&gt;"Sim",NOT(ISNUMBER(D12))),"falta o valor mensal",IF(E12="Sim",0,D12)/F12))))))</f>
         <v/>
       </c>
       <c r="I12" s="25">
@@ -2811,7 +2811,7 @@
         <v/>
       </c>
       <c r="K12" s="46">
-        <f>IF(AND(A12&lt;&gt;"",G12="Sim",OR(NOT(ISNUMBER(F12)),AND(E12&lt;&gt;"Sim",NOT(ISNUMBER(D12))))),1,0)</f>
+        <f>IF(AND(A12&lt;&gt;"",OR(AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),AND(G12="Sim",OR(NOT(ISNUMBER(F12)),AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),AND(E12&lt;&gt;"Sim",NOT(ISNUMBER(D12))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       <c r="F13" s="42" t="n"/>
       <c r="G13" s="45" t="n"/>
       <c r="H13" s="25">
-        <f>IF(OR(A13="",G13&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F13)),F13=0),"faltam as horas planejadas",IF(AND(E13&lt;&gt;"Sim",NOT(ISNUMBER(D13))),"falta o valor mensal",IF(E13="Sim",0,D13)/F13)))</f>
+        <f>IF(A13="","",IF(AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G13&lt;&gt;"Sim","",IF(AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F13)),F13=0),"faltam as horas planejadas",IF(AND(E13&lt;&gt;"Sim",NOT(ISNUMBER(D13))),"falta o valor mensal",IF(E13="Sim",0,D13)/F13))))))</f>
         <v/>
       </c>
       <c r="I13" s="25">
@@ -2836,7 +2836,7 @@
         <v/>
       </c>
       <c r="K13" s="46">
-        <f>IF(AND(A13&lt;&gt;"",G13="Sim",OR(NOT(ISNUMBER(F13)),AND(E13&lt;&gt;"Sim",NOT(ISNUMBER(D13))))),1,0)</f>
+        <f>IF(AND(A13&lt;&gt;"",OR(AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),AND(G13="Sim",OR(NOT(ISNUMBER(F13)),AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),AND(E13&lt;&gt;"Sim",NOT(ISNUMBER(D13))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       <c r="F14" s="42" t="n"/>
       <c r="G14" s="45" t="n"/>
       <c r="H14" s="25">
-        <f>IF(OR(A14="",G14&lt;&gt;"Sim"),"",IF(OR(NOT(ISNUMBER(F14)),F14=0),"faltam as horas planejadas",IF(AND(E14&lt;&gt;"Sim",NOT(ISNUMBER(D14))),"falta o valor mensal",IF(E14="Sim",0,D14)/F14)))</f>
+        <f>IF(A14="","",IF(AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G14&lt;&gt;"Sim","",IF(AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F14)),F14=0),"faltam as horas planejadas",IF(AND(E14&lt;&gt;"Sim",NOT(ISNUMBER(D14))),"falta o valor mensal",IF(E14="Sim",0,D14)/F14))))))</f>
         <v/>
       </c>
       <c r="I14" s="25">
@@ -2861,7 +2861,7 @@
         <v/>
       </c>
       <c r="K14" s="46">
-        <f>IF(AND(A14&lt;&gt;"",G14="Sim",OR(NOT(ISNUMBER(F14)),AND(E14&lt;&gt;"Sim",NOT(ISNUMBER(D14))))),1,0)</f>
+        <f>IF(AND(A14&lt;&gt;"",OR(AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),AND(G14="Sim",OR(NOT(ISNUMBER(F14)),AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),AND(E14&lt;&gt;"Sim",NOT(ISNUMBER(D14))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -1078,7 +1078,7 @@
     </row>
     <row r="3">
       <c r="A3" s="7">
-        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem valor numérico na aba Custos fixos. ","")&amp;IF(SUM(Equipe!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Equipe!$K$5:$K$14)&amp;" pessoa(s) na aba Equipe com valor mensal, horas ou marcação (entra no custo-hora? / já nos fixos?) em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: soma parcial daria custo-hora MENOR do que o real.")</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem valor, com texto ou negativo na aba Custos fixos. ","")&amp;IF(SUM(Equipe!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Equipe!$K$5:$K$14)&amp;" pessoa(s) na aba Equipe com valor mensal, horas ou marcação (entra no custo-hora? / já nos fixos?) em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: soma parcial daria custo-hora MENOR do que o real.")</f>
         <v/>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B14" s="31">
-        <f>Config!$B$7</f>
+        <f>IF(ISNUMBER(Config!$B$7),Config!$B$7,"falta em Config")</f>
         <v>0.3</v>
       </c>
       <c r="C14" s="26" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B15" s="31">
-        <f>Config!$B$8</f>
+        <f>IF(ISNUMBER(Config!$B$8),Config!$B$8,"falta em Config")</f>
         <v>0.11</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="B17" s="29">
-        <f>IF(B16="","",IF(NOT(ISNUMBER(B16)),B16,CEILING(B16,Config!$B$9)))</f>
+        <f>IF(B16="","",IF(NOT(ISNUMBER(B16)),B16,IF(NOT(IF(ISNUMBER(Config!$B$9),Config!$B$9&gt;0,FALSE)),"falta o múltiplo de arredondamento em Config",CEILING(B16,Config!$B$9))))</f>
         <v>340</v>
       </c>
       <c r="C17" s="26" t="inlineStr">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="B21" s="25">
-        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,B13*Config!$B$10/60))</f>
+        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,IF(NOT(IF(ISNUMBER(Config!$B$10),Config!$B$10&gt;0,FALSE)),"falta a duração da consulta em Config",B13*Config!$B$10/60)))</f>
         <v>100</v>
       </c>
       <c r="C21" s="26" t="inlineStr">
@@ -1829,11 +1829,11 @@
         <v>0</v>
       </c>
       <c r="C41" s="34">
-        <f>IF(ISNUMBER($B$12),$B$12*(1-B41),"")</f>
+        <f>IF(AND(ISNUMBER($B$12),IF(ISNUMBER(B41),AND(B41&gt;=0,B41&lt;1),FALSE)),$B$12*(1-B41),"")</f>
         <v>140</v>
       </c>
       <c r="D41" s="25">
-        <f>IF(OR(C41="",C41=0,NOT(ISNUMBER($B$11))),"",$B$11/C41)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(C41),C41&gt;0,FALSE)),NOT(ISNUMBER($B$11))),"",$B$11/C41)</f>
         <v>200</v>
       </c>
       <c r="E41" s="25">
@@ -1847,18 +1847,18 @@
     </row>
     <row r="42">
       <c r="A42" s="24" t="str">
-        <f>"Queda de "&amp;ROUND(B42*100,0)&amp;"%"</f>
+        <f>IF(IF(ISNUMBER(B42),AND(B42&gt;=0,B42&lt;1),FALSE),"Queda de "&amp;ROUND(B42*100,0)&amp;"%","Percentual inválido (0 a 99 %)")</f>
         <v>Queda de 10%</v>
       </c>
       <c r="B42" s="35" t="n">
         <v>0.1</v>
       </c>
       <c r="C42" s="34">
-        <f>IF(ISNUMBER($B$12),$B$12*(1-B42),"")</f>
+        <f>IF(AND(ISNUMBER($B$12),IF(ISNUMBER(B42),AND(B42&gt;=0,B42&lt;1),FALSE)),$B$12*(1-B42),"")</f>
         <v>126</v>
       </c>
       <c r="D42" s="25">
-        <f>IF(OR(C42="",C42=0,NOT(ISNUMBER($B$11))),"",$B$11/C42)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(C42),C42&gt;0,FALSE)),NOT(ISNUMBER($B$11))),"",$B$11/C42)</f>
         <v>222.222222222222</v>
       </c>
       <c r="E42" s="25">
@@ -1872,18 +1872,18 @@
     </row>
     <row r="43">
       <c r="A43" s="24" t="str">
-        <f>"Queda de "&amp;ROUND(B43*100,0)&amp;"%"</f>
+        <f>IF(IF(ISNUMBER(B43),AND(B43&gt;=0,B43&lt;1),FALSE),"Queda de "&amp;ROUND(B43*100,0)&amp;"%","Percentual inválido (0 a 99 %)")</f>
         <v>Queda de 20%</v>
       </c>
       <c r="B43" s="35" t="n">
         <v>0.2</v>
       </c>
       <c r="C43" s="34">
-        <f>IF(ISNUMBER($B$12),$B$12*(1-B43),"")</f>
+        <f>IF(AND(ISNUMBER($B$12),IF(ISNUMBER(B43),AND(B43&gt;=0,B43&lt;1),FALSE)),$B$12*(1-B43),"")</f>
         <v>112</v>
       </c>
       <c r="D43" s="25">
-        <f>IF(OR(C43="",C43=0,NOT(ISNUMBER($B$11))),"",$B$11/C43)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(C43),C43&gt;0,FALSE)),NOT(ISNUMBER($B$11))),"",$B$11/C43)</f>
         <v>250</v>
       </c>
       <c r="E43" s="25">
@@ -1897,18 +1897,18 @@
     </row>
     <row r="44">
       <c r="A44" s="24" t="str">
-        <f>"Queda de "&amp;ROUND(B44*100,0)&amp;"%"</f>
+        <f>IF(IF(ISNUMBER(B44),AND(B44&gt;=0,B44&lt;1),FALSE),"Queda de "&amp;ROUND(B44*100,0)&amp;"%","Percentual inválido (0 a 99 %)")</f>
         <v>Queda de 30%</v>
       </c>
       <c r="B44" s="35" t="n">
         <v>0.3</v>
       </c>
       <c r="C44" s="34">
-        <f>IF(ISNUMBER($B$12),$B$12*(1-B44),"")</f>
+        <f>IF(AND(ISNUMBER($B$12),IF(ISNUMBER(B44),AND(B44&gt;=0,B44&lt;1),FALSE)),$B$12*(1-B44),"")</f>
         <v>98</v>
       </c>
       <c r="D44" s="25">
-        <f>IF(OR(C44="",C44=0,NOT(ISNUMBER($B$11))),"",$B$11/C44)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(C44),C44&gt;0,FALSE)),NOT(ISNUMBER($B$11))),"",$B$11/C44)</f>
         <v>285.714285714286</v>
       </c>
       <c r="E44" s="25">
@@ -1927,14 +1927,14 @@
         </is>
       </c>
       <c r="B45" s="31">
-        <f>IF(OR(C45="",NOT(ISNUMBER($B$12))),"",1-C45/$B$12)</f>
+        <f>IF(OR(C45="",NOT(ISNUMBER($B$12))),"",IF(NOT(IF(ISNUMBER(C45),C45&gt;=0,FALSE)),"horas inválidas",1-C45/$B$12))</f>
         <v>0.323571428571429</v>
       </c>
       <c r="C45" s="36" t="n">
         <v>94.7</v>
       </c>
       <c r="D45" s="25">
-        <f>IF(OR(C45="",C45=0,NOT(ISNUMBER($B$11))),"",$B$11/C45)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(C45),C45&gt;0,FALSE)),NOT(ISNUMBER($B$11))),"",$B$11/C45)</f>
         <v>295.670538542767</v>
       </c>
       <c r="E45" s="25">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="B36" s="29">
-        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*(ISNUMBER(B5:B34)=FALSE))&gt;0,"custo fixo sem valor numérico",SUM(B5:B34))</f>
+        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*((ISNUMBER(B5:B34)=FALSE)+ISNUMBER(B5:B34)*(B5:B34&lt;0)&gt;0))&gt;0,"custo fixo sem valor numérico ou negativo",SUM(B5:B34))</f>
         <v>10000</v>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="H5" s="25">
-        <f>IF(A5="","",IF(AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G5&lt;&gt;"Sim","",IF(AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F5)),F5=0),"faltam as horas planejadas",IF(AND(E5&lt;&gt;"Sim",NOT(ISNUMBER(D5))),"falta o valor mensal",IF(E5="Sim",0,D5)/F5))))))</f>
+        <f>IF(A5="","",IF(AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G5&lt;&gt;"Sim","",IF(AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E5&lt;&gt;"Sim",NOT(IF(ISNUMBER(D5),D5&gt;=0,FALSE))),"falta o valor mensal",IF(E5="Sim",0,D5)/F5))))))</f>
         <v>128.571428571429</v>
       </c>
       <c r="I5" s="25">
@@ -2568,7 +2568,7 @@
         <v>338.983050847458</v>
       </c>
       <c r="K5" s="46">
-        <f>IF(AND(A5&lt;&gt;"",OR(AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),AND(G5="Sim",OR(NOT(ISNUMBER(F5)),AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),AND(E5&lt;&gt;"Sim",NOT(ISNUMBER(D5))))))),1,0)</f>
+        <f>IF(AND(A5&lt;&gt;"",OR(AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),AND(G5="Sim",OR(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),AND(E5&lt;&gt;"Sim",NOT(IF(ISNUMBER(D5),D5&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="H6" s="25">
-        <f>IF(A6="","",IF(AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G6&lt;&gt;"Sim","",IF(AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F6)),F6=0),"faltam as horas planejadas",IF(AND(E6&lt;&gt;"Sim",NOT(ISNUMBER(D6))),"falta o valor mensal",IF(E6="Sim",0,D6)/F6))))))</f>
+        <f>IF(A6="","",IF(AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G6&lt;&gt;"Sim","",IF(AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E6&lt;&gt;"Sim",NOT(IF(ISNUMBER(D6),D6&gt;=0,FALSE))),"falta o valor mensal",IF(E6="Sim",0,D6)/F6))))))</f>
         <v>128.571428571429</v>
       </c>
       <c r="I6" s="25">
@@ -2617,7 +2617,7 @@
         <v>338.983050847458</v>
       </c>
       <c r="K6" s="46">
-        <f>IF(AND(A6&lt;&gt;"",OR(AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),AND(G6="Sim",OR(NOT(ISNUMBER(F6)),AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),AND(E6&lt;&gt;"Sim",NOT(ISNUMBER(D6))))))),1,0)</f>
+        <f>IF(AND(A6&lt;&gt;"",OR(AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),AND(G6="Sim",OR(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),AND(E6&lt;&gt;"Sim",NOT(IF(ISNUMBER(D6),D6&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="H7" s="25">
-        <f>IF(A7="","",IF(AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G7&lt;&gt;"Sim","",IF(AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F7)),F7=0),"faltam as horas planejadas",IF(AND(E7&lt;&gt;"Sim",NOT(ISNUMBER(D7))),"falta o valor mensal",IF(E7="Sim",0,D7)/F7))))))</f>
+        <f>IF(A7="","",IF(AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G7&lt;&gt;"Sim","",IF(AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E7&lt;&gt;"Sim",NOT(IF(ISNUMBER(D7),D7&gt;=0,FALSE))),"falta o valor mensal",IF(E7="Sim",0,D7)/F7))))))</f>
         <v/>
       </c>
       <c r="I7" s="25">
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="K7" s="46">
-        <f>IF(AND(A7&lt;&gt;"",OR(AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),AND(G7="Sim",OR(NOT(ISNUMBER(F7)),AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),AND(E7&lt;&gt;"Sim",NOT(ISNUMBER(D7))))))),1,0)</f>
+        <f>IF(AND(A7&lt;&gt;"",OR(AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),AND(G7="Sim",OR(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),AND(E7&lt;&gt;"Sim",NOT(IF(ISNUMBER(D7),D7&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="H8" s="25">
-        <f>IF(A8="","",IF(AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G8&lt;&gt;"Sim","",IF(AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F8)),F8=0),"faltam as horas planejadas",IF(AND(E8&lt;&gt;"Sim",NOT(ISNUMBER(D8))),"falta o valor mensal",IF(E8="Sim",0,D8)/F8))))))</f>
+        <f>IF(A8="","",IF(AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G8&lt;&gt;"Sim","",IF(AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E8&lt;&gt;"Sim",NOT(IF(ISNUMBER(D8),D8&gt;=0,FALSE))),"falta o valor mensal",IF(E8="Sim",0,D8)/F8))))))</f>
         <v/>
       </c>
       <c r="I8" s="25">
@@ -2711,7 +2711,7 @@
         <v/>
       </c>
       <c r="K8" s="46">
-        <f>IF(AND(A8&lt;&gt;"",OR(AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),AND(G8="Sim",OR(NOT(ISNUMBER(F8)),AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),AND(E8&lt;&gt;"Sim",NOT(ISNUMBER(D8))))))),1,0)</f>
+        <f>IF(AND(A8&lt;&gt;"",OR(AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),AND(G8="Sim",OR(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),AND(E8&lt;&gt;"Sim",NOT(IF(ISNUMBER(D8),D8&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       <c r="F9" s="42" t="n"/>
       <c r="G9" s="45" t="n"/>
       <c r="H9" s="25">
-        <f>IF(A9="","",IF(AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G9&lt;&gt;"Sim","",IF(AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F9)),F9=0),"faltam as horas planejadas",IF(AND(E9&lt;&gt;"Sim",NOT(ISNUMBER(D9))),"falta o valor mensal",IF(E9="Sim",0,D9)/F9))))))</f>
+        <f>IF(A9="","",IF(AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G9&lt;&gt;"Sim","",IF(AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E9&lt;&gt;"Sim",NOT(IF(ISNUMBER(D9),D9&gt;=0,FALSE))),"falta o valor mensal",IF(E9="Sim",0,D9)/F9))))))</f>
         <v/>
       </c>
       <c r="I9" s="25">
@@ -2736,7 +2736,7 @@
         <v/>
       </c>
       <c r="K9" s="46">
-        <f>IF(AND(A9&lt;&gt;"",OR(AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),AND(G9="Sim",OR(NOT(ISNUMBER(F9)),AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),AND(E9&lt;&gt;"Sim",NOT(ISNUMBER(D9))))))),1,0)</f>
+        <f>IF(AND(A9&lt;&gt;"",OR(AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),AND(G9="Sim",OR(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),AND(E9&lt;&gt;"Sim",NOT(IF(ISNUMBER(D9),D9&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       <c r="F10" s="42" t="n"/>
       <c r="G10" s="45" t="n"/>
       <c r="H10" s="25">
-        <f>IF(A10="","",IF(AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G10&lt;&gt;"Sim","",IF(AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F10)),F10=0),"faltam as horas planejadas",IF(AND(E10&lt;&gt;"Sim",NOT(ISNUMBER(D10))),"falta o valor mensal",IF(E10="Sim",0,D10)/F10))))))</f>
+        <f>IF(A10="","",IF(AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G10&lt;&gt;"Sim","",IF(AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E10&lt;&gt;"Sim",NOT(IF(ISNUMBER(D10),D10&gt;=0,FALSE))),"falta o valor mensal",IF(E10="Sim",0,D10)/F10))))))</f>
         <v/>
       </c>
       <c r="I10" s="25">
@@ -2761,7 +2761,7 @@
         <v/>
       </c>
       <c r="K10" s="46">
-        <f>IF(AND(A10&lt;&gt;"",OR(AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),AND(G10="Sim",OR(NOT(ISNUMBER(F10)),AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),AND(E10&lt;&gt;"Sim",NOT(ISNUMBER(D10))))))),1,0)</f>
+        <f>IF(AND(A10&lt;&gt;"",OR(AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),AND(G10="Sim",OR(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),AND(E10&lt;&gt;"Sim",NOT(IF(ISNUMBER(D10),D10&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       <c r="F11" s="42" t="n"/>
       <c r="G11" s="45" t="n"/>
       <c r="H11" s="25">
-        <f>IF(A11="","",IF(AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G11&lt;&gt;"Sim","",IF(AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F11)),F11=0),"faltam as horas planejadas",IF(AND(E11&lt;&gt;"Sim",NOT(ISNUMBER(D11))),"falta o valor mensal",IF(E11="Sim",0,D11)/F11))))))</f>
+        <f>IF(A11="","",IF(AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G11&lt;&gt;"Sim","",IF(AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E11&lt;&gt;"Sim",NOT(IF(ISNUMBER(D11),D11&gt;=0,FALSE))),"falta o valor mensal",IF(E11="Sim",0,D11)/F11))))))</f>
         <v/>
       </c>
       <c r="I11" s="25">
@@ -2786,7 +2786,7 @@
         <v/>
       </c>
       <c r="K11" s="46">
-        <f>IF(AND(A11&lt;&gt;"",OR(AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),AND(G11="Sim",OR(NOT(ISNUMBER(F11)),AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),AND(E11&lt;&gt;"Sim",NOT(ISNUMBER(D11))))))),1,0)</f>
+        <f>IF(AND(A11&lt;&gt;"",OR(AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),AND(G11="Sim",OR(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),AND(E11&lt;&gt;"Sim",NOT(IF(ISNUMBER(D11),D11&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       <c r="F12" s="42" t="n"/>
       <c r="G12" s="45" t="n"/>
       <c r="H12" s="25">
-        <f>IF(A12="","",IF(AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G12&lt;&gt;"Sim","",IF(AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F12)),F12=0),"faltam as horas planejadas",IF(AND(E12&lt;&gt;"Sim",NOT(ISNUMBER(D12))),"falta o valor mensal",IF(E12="Sim",0,D12)/F12))))))</f>
+        <f>IF(A12="","",IF(AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G12&lt;&gt;"Sim","",IF(AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E12&lt;&gt;"Sim",NOT(IF(ISNUMBER(D12),D12&gt;=0,FALSE))),"falta o valor mensal",IF(E12="Sim",0,D12)/F12))))))</f>
         <v/>
       </c>
       <c r="I12" s="25">
@@ -2811,7 +2811,7 @@
         <v/>
       </c>
       <c r="K12" s="46">
-        <f>IF(AND(A12&lt;&gt;"",OR(AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),AND(G12="Sim",OR(NOT(ISNUMBER(F12)),AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),AND(E12&lt;&gt;"Sim",NOT(ISNUMBER(D12))))))),1,0)</f>
+        <f>IF(AND(A12&lt;&gt;"",OR(AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),AND(G12="Sim",OR(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),AND(E12&lt;&gt;"Sim",NOT(IF(ISNUMBER(D12),D12&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       <c r="F13" s="42" t="n"/>
       <c r="G13" s="45" t="n"/>
       <c r="H13" s="25">
-        <f>IF(A13="","",IF(AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G13&lt;&gt;"Sim","",IF(AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F13)),F13=0),"faltam as horas planejadas",IF(AND(E13&lt;&gt;"Sim",NOT(ISNUMBER(D13))),"falta o valor mensal",IF(E13="Sim",0,D13)/F13))))))</f>
+        <f>IF(A13="","",IF(AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G13&lt;&gt;"Sim","",IF(AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E13&lt;&gt;"Sim",NOT(IF(ISNUMBER(D13),D13&gt;=0,FALSE))),"falta o valor mensal",IF(E13="Sim",0,D13)/F13))))))</f>
         <v/>
       </c>
       <c r="I13" s="25">
@@ -2836,7 +2836,7 @@
         <v/>
       </c>
       <c r="K13" s="46">
-        <f>IF(AND(A13&lt;&gt;"",OR(AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),AND(G13="Sim",OR(NOT(ISNUMBER(F13)),AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),AND(E13&lt;&gt;"Sim",NOT(ISNUMBER(D13))))))),1,0)</f>
+        <f>IF(AND(A13&lt;&gt;"",OR(AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),AND(G13="Sim",OR(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),AND(E13&lt;&gt;"Sim",NOT(IF(ISNUMBER(D13),D13&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       <c r="F14" s="42" t="n"/>
       <c r="G14" s="45" t="n"/>
       <c r="H14" s="25">
-        <f>IF(A14="","",IF(AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G14&lt;&gt;"Sim","",IF(AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(OR(NOT(ISNUMBER(F14)),F14=0),"faltam as horas planejadas",IF(AND(E14&lt;&gt;"Sim",NOT(ISNUMBER(D14))),"falta o valor mensal",IF(E14="Sim",0,D14)/F14))))))</f>
+        <f>IF(A14="","",IF(AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G14&lt;&gt;"Sim","",IF(AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E14&lt;&gt;"Sim",NOT(IF(ISNUMBER(D14),D14&gt;=0,FALSE))),"falta o valor mensal",IF(E14="Sim",0,D14)/F14))))))</f>
         <v/>
       </c>
       <c r="I14" s="25">
@@ -2861,7 +2861,7 @@
         <v/>
       </c>
       <c r="K14" s="46">
-        <f>IF(AND(A14&lt;&gt;"",OR(AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),AND(G14="Sim",OR(NOT(ISNUMBER(F14)),AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),AND(E14&lt;&gt;"Sim",NOT(ISNUMBER(D14))))))),1,0)</f>
+        <f>IF(AND(A14&lt;&gt;"",OR(AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),AND(G14="Sim",OR(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),AND(E14&lt;&gt;"Sim",NOT(IF(ISNUMBER(D14),D14&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="H5" s="25">
-        <f>IF(A5="","",IF(AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G5&lt;&gt;"Sim","",IF(AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E5&lt;&gt;"Sim",NOT(IF(ISNUMBER(D5),D5&gt;=0,FALSE))),"falta o valor mensal",IF(E5="Sim",0,D5)/F5))))))</f>
+        <f>IF(NOT(OR(A5&lt;&gt;"",B5&lt;&gt;"",C5&lt;&gt;"",D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;"",G5&lt;&gt;"")),"",IF(A5="","falta o nome",IF(AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G5&lt;&gt;"Sim","",IF(AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E5&lt;&gt;"Sim",NOT(IF(ISNUMBER(D5),D5&gt;=0,FALSE))),"falta o valor mensal",IF(E5="Sim",0,D5)/F5)))))))</f>
         <v>128.571428571429</v>
       </c>
       <c r="I5" s="25">
@@ -2568,7 +2568,7 @@
         <v>338.983050847458</v>
       </c>
       <c r="K5" s="46">
-        <f>IF(AND(A5&lt;&gt;"",OR(AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),AND(G5="Sim",OR(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),AND(E5&lt;&gt;"Sim",NOT(IF(ISNUMBER(D5),D5&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A5&lt;&gt;"",B5&lt;&gt;"",C5&lt;&gt;"",D5&lt;&gt;"",E5&lt;&gt;"",F5&lt;&gt;"",G5&lt;&gt;""),OR(A5="",AND(G5&lt;&gt;"Sim",G5&lt;&gt;"Não"),AND(G5="Sim",OR(NOT(IF(ISNUMBER(F5),F5&gt;0,FALSE)),AND(E5&lt;&gt;"Sim",E5&lt;&gt;"Não"),AND(E5&lt;&gt;"Sim",NOT(IF(ISNUMBER(D5),D5&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="H6" s="25">
-        <f>IF(A6="","",IF(AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G6&lt;&gt;"Sim","",IF(AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E6&lt;&gt;"Sim",NOT(IF(ISNUMBER(D6),D6&gt;=0,FALSE))),"falta o valor mensal",IF(E6="Sim",0,D6)/F6))))))</f>
+        <f>IF(NOT(OR(A6&lt;&gt;"",B6&lt;&gt;"",C6&lt;&gt;"",D6&lt;&gt;"",E6&lt;&gt;"",F6&lt;&gt;"",G6&lt;&gt;"")),"",IF(A6="","falta o nome",IF(AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G6&lt;&gt;"Sim","",IF(AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E6&lt;&gt;"Sim",NOT(IF(ISNUMBER(D6),D6&gt;=0,FALSE))),"falta o valor mensal",IF(E6="Sim",0,D6)/F6)))))))</f>
         <v>128.571428571429</v>
       </c>
       <c r="I6" s="25">
@@ -2617,7 +2617,7 @@
         <v>338.983050847458</v>
       </c>
       <c r="K6" s="46">
-        <f>IF(AND(A6&lt;&gt;"",OR(AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),AND(G6="Sim",OR(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),AND(E6&lt;&gt;"Sim",NOT(IF(ISNUMBER(D6),D6&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A6&lt;&gt;"",B6&lt;&gt;"",C6&lt;&gt;"",D6&lt;&gt;"",E6&lt;&gt;"",F6&lt;&gt;"",G6&lt;&gt;""),OR(A6="",AND(G6&lt;&gt;"Sim",G6&lt;&gt;"Não"),AND(G6="Sim",OR(NOT(IF(ISNUMBER(F6),F6&gt;0,FALSE)),AND(E6&lt;&gt;"Sim",E6&lt;&gt;"Não"),AND(E6&lt;&gt;"Sim",NOT(IF(ISNUMBER(D6),D6&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="H7" s="25">
-        <f>IF(A7="","",IF(AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G7&lt;&gt;"Sim","",IF(AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E7&lt;&gt;"Sim",NOT(IF(ISNUMBER(D7),D7&gt;=0,FALSE))),"falta o valor mensal",IF(E7="Sim",0,D7)/F7))))))</f>
+        <f>IF(NOT(OR(A7&lt;&gt;"",B7&lt;&gt;"",C7&lt;&gt;"",D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;"",G7&lt;&gt;"")),"",IF(A7="","falta o nome",IF(AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G7&lt;&gt;"Sim","",IF(AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E7&lt;&gt;"Sim",NOT(IF(ISNUMBER(D7),D7&gt;=0,FALSE))),"falta o valor mensal",IF(E7="Sim",0,D7)/F7)))))))</f>
         <v/>
       </c>
       <c r="I7" s="25">
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="K7" s="46">
-        <f>IF(AND(A7&lt;&gt;"",OR(AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),AND(G7="Sim",OR(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),AND(E7&lt;&gt;"Sim",NOT(IF(ISNUMBER(D7),D7&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A7&lt;&gt;"",B7&lt;&gt;"",C7&lt;&gt;"",D7&lt;&gt;"",E7&lt;&gt;"",F7&lt;&gt;"",G7&lt;&gt;""),OR(A7="",AND(G7&lt;&gt;"Sim",G7&lt;&gt;"Não"),AND(G7="Sim",OR(NOT(IF(ISNUMBER(F7),F7&gt;0,FALSE)),AND(E7&lt;&gt;"Sim",E7&lt;&gt;"Não"),AND(E7&lt;&gt;"Sim",NOT(IF(ISNUMBER(D7),D7&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="H8" s="25">
-        <f>IF(A8="","",IF(AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G8&lt;&gt;"Sim","",IF(AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E8&lt;&gt;"Sim",NOT(IF(ISNUMBER(D8),D8&gt;=0,FALSE))),"falta o valor mensal",IF(E8="Sim",0,D8)/F8))))))</f>
+        <f>IF(NOT(OR(A8&lt;&gt;"",B8&lt;&gt;"",C8&lt;&gt;"",D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;"",G8&lt;&gt;"")),"",IF(A8="","falta o nome",IF(AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G8&lt;&gt;"Sim","",IF(AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E8&lt;&gt;"Sim",NOT(IF(ISNUMBER(D8),D8&gt;=0,FALSE))),"falta o valor mensal",IF(E8="Sim",0,D8)/F8)))))))</f>
         <v/>
       </c>
       <c r="I8" s="25">
@@ -2711,7 +2711,7 @@
         <v/>
       </c>
       <c r="K8" s="46">
-        <f>IF(AND(A8&lt;&gt;"",OR(AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),AND(G8="Sim",OR(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),AND(E8&lt;&gt;"Sim",NOT(IF(ISNUMBER(D8),D8&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A8&lt;&gt;"",B8&lt;&gt;"",C8&lt;&gt;"",D8&lt;&gt;"",E8&lt;&gt;"",F8&lt;&gt;"",G8&lt;&gt;""),OR(A8="",AND(G8&lt;&gt;"Sim",G8&lt;&gt;"Não"),AND(G8="Sim",OR(NOT(IF(ISNUMBER(F8),F8&gt;0,FALSE)),AND(E8&lt;&gt;"Sim",E8&lt;&gt;"Não"),AND(E8&lt;&gt;"Sim",NOT(IF(ISNUMBER(D8),D8&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       <c r="F9" s="42" t="n"/>
       <c r="G9" s="45" t="n"/>
       <c r="H9" s="25">
-        <f>IF(A9="","",IF(AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G9&lt;&gt;"Sim","",IF(AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E9&lt;&gt;"Sim",NOT(IF(ISNUMBER(D9),D9&gt;=0,FALSE))),"falta o valor mensal",IF(E9="Sim",0,D9)/F9))))))</f>
+        <f>IF(NOT(OR(A9&lt;&gt;"",B9&lt;&gt;"",C9&lt;&gt;"",D9&lt;&gt;"",E9&lt;&gt;"",F9&lt;&gt;"",G9&lt;&gt;"")),"",IF(A9="","falta o nome",IF(AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G9&lt;&gt;"Sim","",IF(AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E9&lt;&gt;"Sim",NOT(IF(ISNUMBER(D9),D9&gt;=0,FALSE))),"falta o valor mensal",IF(E9="Sim",0,D9)/F9)))))))</f>
         <v/>
       </c>
       <c r="I9" s="25">
@@ -2736,7 +2736,7 @@
         <v/>
       </c>
       <c r="K9" s="46">
-        <f>IF(AND(A9&lt;&gt;"",OR(AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),AND(G9="Sim",OR(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),AND(E9&lt;&gt;"Sim",NOT(IF(ISNUMBER(D9),D9&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A9&lt;&gt;"",B9&lt;&gt;"",C9&lt;&gt;"",D9&lt;&gt;"",E9&lt;&gt;"",F9&lt;&gt;"",G9&lt;&gt;""),OR(A9="",AND(G9&lt;&gt;"Sim",G9&lt;&gt;"Não"),AND(G9="Sim",OR(NOT(IF(ISNUMBER(F9),F9&gt;0,FALSE)),AND(E9&lt;&gt;"Sim",E9&lt;&gt;"Não"),AND(E9&lt;&gt;"Sim",NOT(IF(ISNUMBER(D9),D9&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       <c r="F10" s="42" t="n"/>
       <c r="G10" s="45" t="n"/>
       <c r="H10" s="25">
-        <f>IF(A10="","",IF(AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G10&lt;&gt;"Sim","",IF(AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E10&lt;&gt;"Sim",NOT(IF(ISNUMBER(D10),D10&gt;=0,FALSE))),"falta o valor mensal",IF(E10="Sim",0,D10)/F10))))))</f>
+        <f>IF(NOT(OR(A10&lt;&gt;"",B10&lt;&gt;"",C10&lt;&gt;"",D10&lt;&gt;"",E10&lt;&gt;"",F10&lt;&gt;"",G10&lt;&gt;"")),"",IF(A10="","falta o nome",IF(AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G10&lt;&gt;"Sim","",IF(AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E10&lt;&gt;"Sim",NOT(IF(ISNUMBER(D10),D10&gt;=0,FALSE))),"falta o valor mensal",IF(E10="Sim",0,D10)/F10)))))))</f>
         <v/>
       </c>
       <c r="I10" s="25">
@@ -2761,7 +2761,7 @@
         <v/>
       </c>
       <c r="K10" s="46">
-        <f>IF(AND(A10&lt;&gt;"",OR(AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),AND(G10="Sim",OR(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),AND(E10&lt;&gt;"Sim",NOT(IF(ISNUMBER(D10),D10&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A10&lt;&gt;"",B10&lt;&gt;"",C10&lt;&gt;"",D10&lt;&gt;"",E10&lt;&gt;"",F10&lt;&gt;"",G10&lt;&gt;""),OR(A10="",AND(G10&lt;&gt;"Sim",G10&lt;&gt;"Não"),AND(G10="Sim",OR(NOT(IF(ISNUMBER(F10),F10&gt;0,FALSE)),AND(E10&lt;&gt;"Sim",E10&lt;&gt;"Não"),AND(E10&lt;&gt;"Sim",NOT(IF(ISNUMBER(D10),D10&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       <c r="F11" s="42" t="n"/>
       <c r="G11" s="45" t="n"/>
       <c r="H11" s="25">
-        <f>IF(A11="","",IF(AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G11&lt;&gt;"Sim","",IF(AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E11&lt;&gt;"Sim",NOT(IF(ISNUMBER(D11),D11&gt;=0,FALSE))),"falta o valor mensal",IF(E11="Sim",0,D11)/F11))))))</f>
+        <f>IF(NOT(OR(A11&lt;&gt;"",B11&lt;&gt;"",C11&lt;&gt;"",D11&lt;&gt;"",E11&lt;&gt;"",F11&lt;&gt;"",G11&lt;&gt;"")),"",IF(A11="","falta o nome",IF(AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G11&lt;&gt;"Sim","",IF(AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E11&lt;&gt;"Sim",NOT(IF(ISNUMBER(D11),D11&gt;=0,FALSE))),"falta o valor mensal",IF(E11="Sim",0,D11)/F11)))))))</f>
         <v/>
       </c>
       <c r="I11" s="25">
@@ -2786,7 +2786,7 @@
         <v/>
       </c>
       <c r="K11" s="46">
-        <f>IF(AND(A11&lt;&gt;"",OR(AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),AND(G11="Sim",OR(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),AND(E11&lt;&gt;"Sim",NOT(IF(ISNUMBER(D11),D11&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A11&lt;&gt;"",B11&lt;&gt;"",C11&lt;&gt;"",D11&lt;&gt;"",E11&lt;&gt;"",F11&lt;&gt;"",G11&lt;&gt;""),OR(A11="",AND(G11&lt;&gt;"Sim",G11&lt;&gt;"Não"),AND(G11="Sim",OR(NOT(IF(ISNUMBER(F11),F11&gt;0,FALSE)),AND(E11&lt;&gt;"Sim",E11&lt;&gt;"Não"),AND(E11&lt;&gt;"Sim",NOT(IF(ISNUMBER(D11),D11&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       <c r="F12" s="42" t="n"/>
       <c r="G12" s="45" t="n"/>
       <c r="H12" s="25">
-        <f>IF(A12="","",IF(AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G12&lt;&gt;"Sim","",IF(AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E12&lt;&gt;"Sim",NOT(IF(ISNUMBER(D12),D12&gt;=0,FALSE))),"falta o valor mensal",IF(E12="Sim",0,D12)/F12))))))</f>
+        <f>IF(NOT(OR(A12&lt;&gt;"",B12&lt;&gt;"",C12&lt;&gt;"",D12&lt;&gt;"",E12&lt;&gt;"",F12&lt;&gt;"",G12&lt;&gt;"")),"",IF(A12="","falta o nome",IF(AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G12&lt;&gt;"Sim","",IF(AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E12&lt;&gt;"Sim",NOT(IF(ISNUMBER(D12),D12&gt;=0,FALSE))),"falta o valor mensal",IF(E12="Sim",0,D12)/F12)))))))</f>
         <v/>
       </c>
       <c r="I12" s="25">
@@ -2811,7 +2811,7 @@
         <v/>
       </c>
       <c r="K12" s="46">
-        <f>IF(AND(A12&lt;&gt;"",OR(AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),AND(G12="Sim",OR(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),AND(E12&lt;&gt;"Sim",NOT(IF(ISNUMBER(D12),D12&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A12&lt;&gt;"",B12&lt;&gt;"",C12&lt;&gt;"",D12&lt;&gt;"",E12&lt;&gt;"",F12&lt;&gt;"",G12&lt;&gt;""),OR(A12="",AND(G12&lt;&gt;"Sim",G12&lt;&gt;"Não"),AND(G12="Sim",OR(NOT(IF(ISNUMBER(F12),F12&gt;0,FALSE)),AND(E12&lt;&gt;"Sim",E12&lt;&gt;"Não"),AND(E12&lt;&gt;"Sim",NOT(IF(ISNUMBER(D12),D12&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       <c r="F13" s="42" t="n"/>
       <c r="G13" s="45" t="n"/>
       <c r="H13" s="25">
-        <f>IF(A13="","",IF(AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G13&lt;&gt;"Sim","",IF(AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E13&lt;&gt;"Sim",NOT(IF(ISNUMBER(D13),D13&gt;=0,FALSE))),"falta o valor mensal",IF(E13="Sim",0,D13)/F13))))))</f>
+        <f>IF(NOT(OR(A13&lt;&gt;"",B13&lt;&gt;"",C13&lt;&gt;"",D13&lt;&gt;"",E13&lt;&gt;"",F13&lt;&gt;"",G13&lt;&gt;"")),"",IF(A13="","falta o nome",IF(AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G13&lt;&gt;"Sim","",IF(AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E13&lt;&gt;"Sim",NOT(IF(ISNUMBER(D13),D13&gt;=0,FALSE))),"falta o valor mensal",IF(E13="Sim",0,D13)/F13)))))))</f>
         <v/>
       </c>
       <c r="I13" s="25">
@@ -2836,7 +2836,7 @@
         <v/>
       </c>
       <c r="K13" s="46">
-        <f>IF(AND(A13&lt;&gt;"",OR(AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),AND(G13="Sim",OR(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),AND(E13&lt;&gt;"Sim",NOT(IF(ISNUMBER(D13),D13&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A13&lt;&gt;"",B13&lt;&gt;"",C13&lt;&gt;"",D13&lt;&gt;"",E13&lt;&gt;"",F13&lt;&gt;"",G13&lt;&gt;""),OR(A13="",AND(G13&lt;&gt;"Sim",G13&lt;&gt;"Não"),AND(G13="Sim",OR(NOT(IF(ISNUMBER(F13),F13&gt;0,FALSE)),AND(E13&lt;&gt;"Sim",E13&lt;&gt;"Não"),AND(E13&lt;&gt;"Sim",NOT(IF(ISNUMBER(D13),D13&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       <c r="F14" s="42" t="n"/>
       <c r="G14" s="45" t="n"/>
       <c r="H14" s="25">
-        <f>IF(A14="","",IF(AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G14&lt;&gt;"Sim","",IF(AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E14&lt;&gt;"Sim",NOT(IF(ISNUMBER(D14),D14&gt;=0,FALSE))),"falta o valor mensal",IF(E14="Sim",0,D14)/F14))))))</f>
+        <f>IF(NOT(OR(A14&lt;&gt;"",B14&lt;&gt;"",C14&lt;&gt;"",D14&lt;&gt;"",E14&lt;&gt;"",F14&lt;&gt;"",G14&lt;&gt;"")),"",IF(A14="","falta o nome",IF(AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),"falta: entra no custo-hora?",IF(G14&lt;&gt;"Sim","",IF(AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),"falta: já está nos custos fixos?",IF(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),"faltam as horas planejadas",IF(AND(E14&lt;&gt;"Sim",NOT(IF(ISNUMBER(D14),D14&gt;=0,FALSE))),"falta o valor mensal",IF(E14="Sim",0,D14)/F14)))))))</f>
         <v/>
       </c>
       <c r="I14" s="25">
@@ -2861,7 +2861,7 @@
         <v/>
       </c>
       <c r="K14" s="46">
-        <f>IF(AND(A14&lt;&gt;"",OR(AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),AND(G14="Sim",OR(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),AND(E14&lt;&gt;"Sim",NOT(IF(ISNUMBER(D14),D14&gt;=0,FALSE))))))),1,0)</f>
+        <f>IF(AND(OR(A14&lt;&gt;"",B14&lt;&gt;"",C14&lt;&gt;"",D14&lt;&gt;"",E14&lt;&gt;"",F14&lt;&gt;"",G14&lt;&gt;""),OR(A14="",AND(G14&lt;&gt;"Sim",G14&lt;&gt;"Não"),AND(G14="Sim",OR(NOT(IF(ISNUMBER(F14),F14&gt;0,FALSE)),AND(E14&lt;&gt;"Sim",E14&lt;&gt;"Não"),AND(E14&lt;&gt;"Sim",NOT(IF(ISNUMBER(D14),D14&gt;=0,FALSE))))))),1,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/05-custo-da-hora.xlsx
@@ -1078,7 +1078,7 @@
     </row>
     <row r="3">
       <c r="A3" s="7">
-        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem valor, com texto ou negativo na aba Custos fixos. ","")&amp;IF(SUM(Equipe!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Equipe!$K$5:$K$14)&amp;" pessoa(s) na aba Equipe com valor mensal, horas ou marcação (entra no custo-hora? / já nos fixos?) em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: soma parcial daria custo-hora MENOR do que o real.")</f>
+        <f>IF((SUM(Equipe!$K$5:$K$14)+IF(ISNUMBER('Custos fixos'!$B$36),0,1))=0,"",IF(IF(ISNUMBER('Custos fixos'!$B$36),0,1)&gt;0,"Atenção: há custo fixo sem descrição, sem valor, com texto ou negativo na aba Custos fixos. ","")&amp;IF(SUM(Equipe!$K$5:$K$14)&gt;0,"Atenção: "&amp;SUM(Equipe!$K$5:$K$14)&amp;" pessoa(s) na aba Equipe com valor mensal, horas ou marcação (entra no custo-hora? / já nos fixos?) em branco. ","")&amp;"Custo do mês, custo-hora e hora mínima ficam como 'cadastro incompleto' até você completar: soma parcial daria custo-hora MENOR do que o real.")</f>
         <v/>
       </c>
     </row>
@@ -1471,11 +1471,11 @@
         <v>Dra. Carolina Mendes</v>
       </c>
       <c r="B26" s="24" t="str">
-        <f>IF(Equipe!$A$5="","",Equipe!$B$5)</f>
+        <f>IF(OR(Equipe!$A$5="",Equipe!$B$5=""),"",Equipe!$B$5)</f>
         <v>Sócia · clínica médica</v>
       </c>
       <c r="C26" s="32" t="str">
-        <f>IF(Equipe!$A$5="","",Equipe!$C$5)</f>
+        <f>IF(OR(Equipe!$A$5="",Equipe!$C$5=""),"",Equipe!$C$5)</f>
         <v>Pró-labore</v>
       </c>
       <c r="D26" s="30">
@@ -1501,11 +1501,11 @@
         <v>Dr. Paulo Andrade</v>
       </c>
       <c r="B27" s="24" t="str">
-        <f>IF(Equipe!$A$6="","",Equipe!$B$6)</f>
+        <f>IF(OR(Equipe!$A$6="",Equipe!$B$6=""),"",Equipe!$B$6)</f>
         <v>Sócio · cardiologia</v>
       </c>
       <c r="C27" s="32" t="str">
-        <f>IF(Equipe!$A$6="","",Equipe!$C$6)</f>
+        <f>IF(OR(Equipe!$A$6="",Equipe!$C$6=""),"",Equipe!$C$6)</f>
         <v>Pró-labore</v>
       </c>
       <c r="D27" s="30">
@@ -1531,11 +1531,11 @@
         <v>Dra. Renata Sousa</v>
       </c>
       <c r="B28" s="24" t="str">
-        <f>IF(Equipe!$A$7="","",Equipe!$B$7)</f>
+        <f>IF(OR(Equipe!$A$7="",Equipe!$B$7=""),"",Equipe!$B$7)</f>
         <v>Médica parceira · endocrinologia</v>
       </c>
       <c r="C28" s="32" t="str">
-        <f>IF(Equipe!$A$7="","",Equipe!$C$7)</f>
+        <f>IF(OR(Equipe!$A$7="",Equipe!$C$7=""),"",Equipe!$C$7)</f>
         <v>Repasse</v>
       </c>
       <c r="D28" s="30">
@@ -1561,11 +1561,11 @@
         <v>Bruna Carvalho</v>
       </c>
       <c r="B29" s="24" t="str">
-        <f>IF(Equipe!$A$8="","",Equipe!$B$8)</f>
+        <f>IF(OR(Equipe!$A$8="",Equipe!$B$8=""),"",Equipe!$B$8)</f>
         <v>Recepcionista (CLT)</v>
       </c>
       <c r="C29" s="32" t="str">
-        <f>IF(Equipe!$A$8="","",Equipe!$C$8)</f>
+        <f>IF(OR(Equipe!$A$8="",Equipe!$C$8=""),"",Equipe!$C$8)</f>
         <v>Salário</v>
       </c>
       <c r="D29" s="30">
@@ -1591,11 +1591,11 @@
         <v/>
       </c>
       <c r="B30" s="24">
-        <f>IF(Equipe!$A$9="","",Equipe!$B$9)</f>
+        <f>IF(OR(Equipe!$A$9="",Equipe!$B$9=""),"",Equipe!$B$9)</f>
         <v/>
       </c>
       <c r="C30" s="32">
-        <f>IF(Equipe!$A$9="","",Equipe!$C$9)</f>
+        <f>IF(OR(Equipe!$A$9="",Equipe!$C$9=""),"",Equipe!$C$9)</f>
         <v/>
       </c>
       <c r="D30" s="30">
@@ -1621,11 +1621,11 @@
         <v/>
       </c>
       <c r="B31" s="24">
-        <f>IF(Equipe!$A$10="","",Equipe!$B$10)</f>
+        <f>IF(OR(Equipe!$A$10="",Equipe!$B$10=""),"",Equipe!$B$10)</f>
         <v/>
       </c>
       <c r="C31" s="32">
-        <f>IF(Equipe!$A$10="","",Equipe!$C$10)</f>
+        <f>IF(OR(Equipe!$A$10="",Equipe!$C$10=""),"",Equipe!$C$10)</f>
         <v/>
       </c>
       <c r="D31" s="30">
@@ -1651,11 +1651,11 @@
         <v/>
       </c>
       <c r="B32" s="24">
-        <f>IF(Equipe!$A$11="","",Equipe!$B$11)</f>
+        <f>IF(OR(Equipe!$A$11="",Equipe!$B$11=""),"",Equipe!$B$11)</f>
         <v/>
       </c>
       <c r="C32" s="32">
-        <f>IF(Equipe!$A$11="","",Equipe!$C$11)</f>
+        <f>IF(OR(Equipe!$A$11="",Equipe!$C$11=""),"",Equipe!$C$11)</f>
         <v/>
       </c>
       <c r="D32" s="30">
@@ -1681,11 +1681,11 @@
         <v/>
       </c>
       <c r="B33" s="24">
-        <f>IF(Equipe!$A$12="","",Equipe!$B$12)</f>
+        <f>IF(OR(Equipe!$A$12="",Equipe!$B$12=""),"",Equipe!$B$12)</f>
         <v/>
       </c>
       <c r="C33" s="32">
-        <f>IF(Equipe!$A$12="","",Equipe!$C$12)</f>
+        <f>IF(OR(Equipe!$A$12="",Equipe!$C$12=""),"",Equipe!$C$12)</f>
         <v/>
       </c>
       <c r="D33" s="30">
@@ -1711,11 +1711,11 @@
         <v/>
       </c>
       <c r="B34" s="24">
-        <f>IF(Equipe!$A$13="","",Equipe!$B$13)</f>
+        <f>IF(OR(Equipe!$A$13="",Equipe!$B$13=""),"",Equipe!$B$13)</f>
         <v/>
       </c>
       <c r="C34" s="32">
-        <f>IF(Equipe!$A$13="","",Equipe!$C$13)</f>
+        <f>IF(OR(Equipe!$A$13="",Equipe!$C$13=""),"",Equipe!$C$13)</f>
         <v/>
       </c>
       <c r="D34" s="30">
@@ -1741,11 +1741,11 @@
         <v/>
       </c>
       <c r="B35" s="24">
-        <f>IF(Equipe!$A$14="","",Equipe!$B$14)</f>
+        <f>IF(OR(Equipe!$A$14="",Equipe!$B$14=""),"",Equipe!$B$14)</f>
         <v/>
       </c>
       <c r="C35" s="32">
-        <f>IF(Equipe!$A$14="","",Equipe!$C$14)</f>
+        <f>IF(OR(Equipe!$A$14="",Equipe!$C$14=""),"",Equipe!$C$14)</f>
         <v/>
       </c>
       <c r="D35" s="30">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="B36" s="29">
-        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*((ISNUMBER(B5:B34)=FALSE)+ISNUMBER(B5:B34)*(B5:B34&lt;0)&gt;0))&gt;0,"custo fixo sem valor numérico ou negativo",SUM(B5:B34))</f>
+        <f>IF(SUMPRODUCT(((A5:A34&lt;&gt;"")+(B5:B34&lt;&gt;"")&gt;0)*((A5:A34="")+(ISNUMBER(B5:B34)=FALSE)+ISNUMBER(B5:B34)*(B5:B34&lt;0)&gt;0))&gt;0,"custo fixo sem descrição, sem valor numérico ou negativo",SUM(B5:B34))</f>
         <v>10000</v>
       </c>
     </row>
